--- a/docs/reports/CEG.xlsx
+++ b/docs/reports/CEG.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SWS Valuation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Target Price" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financial Model" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="6" state="visible" r:id="rId6"/>
@@ -144,7 +144,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,20 +160,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="5" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -183,6 +179,7 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="7" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="9" fillId="4" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="169" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -570,7 +567,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Utilities · Standard (2-Stage FCFE) · generated 2026-07-08 · data: yfinance</t>
+          <t>Utilities · Standard (forward multiples + DCF) · generated 2026-10-13 · data: Yahoo snapshot as of 2026-07-08</t>
         </is>
       </c>
     </row>
@@ -588,7 +585,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>DCF value per share</t>
+          <t>DCF value per share (one lens)</t>
         </is>
       </c>
       <c r="B5" s="4">
@@ -610,11 +607,11 @@
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Blended fair value (report)</t>
+          <t>12-month price target (report)</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>169.3480035875697</v>
+        <v>278.3245544984664</v>
       </c>
     </row>
     <row r="8">
@@ -702,7 +699,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -744,16 +741,16 @@
           <t>Ordinary Shares Number</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>327</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>317</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>312.838</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>312.29008</v>
       </c>
     </row>
@@ -763,16 +760,16 @@
           <t>Share Issued</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>327</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>317</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>312.838</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>312.29008</v>
       </c>
     </row>
@@ -782,16 +779,16 @@
           <t>Net Debt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>5346</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>8893</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>5390</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>5351</v>
       </c>
     </row>
@@ -801,16 +798,16 @@
           <t>Total Debt</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>5768</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>9261</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>8412</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>8992</v>
       </c>
     </row>
@@ -820,16 +817,16 @@
           <t>Tangible Book Value</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>10971</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>10500</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>12746</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>14097</v>
       </c>
     </row>
@@ -839,16 +836,16 @@
           <t>Invested Capital</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>16786</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>20186</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>21578</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>23509</v>
       </c>
     </row>
@@ -858,16 +855,16 @@
           <t>Working Capital</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>1521</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>1980</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>3930</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>4175</v>
       </c>
     </row>
@@ -877,16 +874,16 @@
           <t>Net Tangible Assets</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>10971</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>10500</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>12746</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>14097</v>
       </c>
     </row>
@@ -896,16 +893,16 @@
           <t>Common Stock Equity</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>11018</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>10925</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>13166</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>14517</v>
       </c>
     </row>
@@ -915,16 +912,16 @@
           <t>Total Capitalization</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>15484</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>18421</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>20550</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>21767</v>
       </c>
     </row>
@@ -934,16 +931,16 @@
           <t>Total Equity Gross Minority Interest</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>11372</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>11286</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>13539</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>14853</v>
       </c>
     </row>
@@ -953,16 +950,16 @@
           <t>Minority Interest</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>354</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>361</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>373</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>336</v>
       </c>
     </row>
@@ -972,16 +969,16 @@
           <t>Stockholders Equity</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>11018</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>10925</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>13166</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>14517</v>
       </c>
     </row>
@@ -991,7 +988,7 @@
           <t>Other Equity Interest</t>
         </is>
       </c>
-      <c r="B18" s="29" t="n">
+      <c r="B18" s="25" t="n">
         <v>11250</v>
       </c>
     </row>
@@ -1001,16 +998,16 @@
           <t>Gains Losses Not Affecting Retained Earnings</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-1760</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-2191</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>-2302</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>-2425</v>
       </c>
     </row>
@@ -1020,16 +1017,16 @@
           <t>Other Equity Adjustments</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>-1760</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>-2191</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>-2302</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>-2425</v>
       </c>
     </row>
@@ -1039,16 +1036,16 @@
           <t>Retained Earnings</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>-496</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>761</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>4066</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>5899</v>
       </c>
     </row>
@@ -1058,16 +1055,16 @@
           <t>Capital Stock</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>13274</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>12355</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>11402</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>11043</v>
       </c>
     </row>
@@ -1077,16 +1074,16 @@
           <t>Common Stock</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>13274</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>12355</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>11402</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>11043</v>
       </c>
     </row>
@@ -1096,16 +1093,16 @@
           <t>Total Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>35537</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>39472</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>39387</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>42396</v>
       </c>
     </row>
@@ -1115,16 +1112,16 @@
           <t>Total Non Current Liabilities Net Minority Interest</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>27698</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>33153</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>32541</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>34452</v>
       </c>
     </row>
@@ -1134,16 +1131,16 @@
           <t>Other Non Current Liabilities</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>2408</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>2421</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>2585</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>2740</v>
       </c>
     </row>
@@ -1153,16 +1150,16 @@
           <t>Derivative Product Liabilities</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>983</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>419</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>399</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>414</v>
       </c>
     </row>
@@ -1172,16 +1169,16 @@
           <t>Employee Benefits</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>1214</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>1802</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>1875</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>1977</v>
       </c>
     </row>
@@ -1191,16 +1188,16 @@
           <t>Non Current Pension And Other Postretirement Benefit Plans</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>1214</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>1802</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>1875</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>1977</v>
       </c>
     </row>
@@ -1210,10 +1207,10 @@
           <t>Dueto Related Parties Non Current</t>
         </is>
       </c>
-      <c r="B30" s="29" t="n">
+      <c r="B30" s="25" t="n">
         <v>3357</v>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1223,16 +1220,16 @@
           <t>Tradeand Other Payables Non Current</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>2897</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>3688</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>4518</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>5334</v>
       </c>
     </row>
@@ -1242,16 +1239,16 @@
           <t>Non Current Deferred Liabilities</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>3031</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>3209</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>3331</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>3544</v>
       </c>
     </row>
@@ -1261,16 +1258,16 @@
           <t>Non Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>3031</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>3209</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>3331</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>3544</v>
       </c>
     </row>
@@ -1280,16 +1277,16 @@
           <t>Long Term Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>4466</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>7496</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>7384</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>7250</v>
       </c>
     </row>
@@ -1299,16 +1296,16 @@
           <t>Long Term Debt</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>4466</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>7496</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>7384</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>7250</v>
       </c>
     </row>
@@ -1318,16 +1315,16 @@
           <t>Long Term Provisions</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>12699</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>14118</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>12449</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>13193</v>
       </c>
     </row>
@@ -1337,16 +1334,16 @@
           <t>Current Liabilities</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>7839</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>6319</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>6846</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>7944</v>
       </c>
     </row>
@@ -1356,16 +1353,16 @@
           <t>Other Current Liabilities</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>2803</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>1942</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>1875</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>1908</v>
       </c>
     </row>
@@ -1375,16 +1372,16 @@
           <t>Current Debt And Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>1302</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>1765</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>1028</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>1742</v>
       </c>
     </row>
@@ -1394,16 +1391,16 @@
           <t>Current Debt</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>1302</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>1765</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>1028</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>1742</v>
       </c>
     </row>
@@ -1413,16 +1410,16 @@
           <t>Other Current Borrowings</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>1302</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>1765</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>1028</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>1742</v>
       </c>
     </row>
@@ -1432,10 +1429,10 @@
           <t>Pensionand Other Post Retirement Benefit Plans Current</t>
         </is>
       </c>
-      <c r="E42" s="29" t="n">
+      <c r="E42" s="25" t="n">
         <v>907</v>
       </c>
-      <c r="F42" s="29" t="n">
+      <c r="F42" s="25" t="n">
         <v>920</v>
       </c>
     </row>
@@ -1445,16 +1442,16 @@
           <t>Payables And Accrued Expenses</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>3734</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>2612</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>3036</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>3374</v>
       </c>
     </row>
@@ -1464,16 +1461,16 @@
           <t>Current Accrued Expenses</t>
         </is>
       </c>
-      <c r="B44" s="29" t="n">
+      <c r="B44" s="25" t="n">
         <v>737</v>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>906</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>435</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>315</v>
       </c>
     </row>
@@ -1483,10 +1480,10 @@
           <t>Interest Payable</t>
         </is>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>435</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>315</v>
       </c>
     </row>
@@ -1496,16 +1493,16 @@
           <t>Payables</t>
         </is>
       </c>
-      <c r="B46" s="29" t="n">
+      <c r="B46" s="25" t="n">
         <v>1888</v>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>2828</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>2601</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>3059</v>
       </c>
     </row>
@@ -1515,10 +1512,10 @@
           <t>Dueto Related Parties Current</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="25" t="n">
         <v>131</v>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1528,10 +1525,10 @@
           <t>Total Tax Payable</t>
         </is>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>232</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>246</v>
       </c>
     </row>
@@ -1541,16 +1538,16 @@
           <t>Accounts Payable</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="25" t="n">
         <v>1757</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>2828</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>2369</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>2813</v>
       </c>
     </row>
@@ -1560,16 +1557,16 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>46909</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>50758</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>52926</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>57249</v>
       </c>
     </row>
@@ -1579,16 +1576,16 @@
           <t>Total Non Current Assets</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>37549</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>42459</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>42150</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>45130</v>
       </c>
     </row>
@@ -1598,16 +1595,16 @@
           <t>Other Non Current Assets</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>16173</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>18308</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>19483</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>21479</v>
       </c>
     </row>
@@ -1617,10 +1614,10 @@
           <t>Defined Pension Benefit</t>
         </is>
       </c>
-      <c r="B53" s="29" t="n">
+      <c r="B53" s="25" t="n">
         <v>1683</v>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1630,16 +1627,16 @@
           <t>Non Current Deferred Assets</t>
         </is>
       </c>
-      <c r="B54" s="29" t="n">
+      <c r="B54" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1649,16 +1646,16 @@
           <t>Non Current Deferred Taxes Assets</t>
         </is>
       </c>
-      <c r="B55" s="29" t="n">
+      <c r="B55" s="25" t="n">
         <v>32</v>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1668,16 +1665,16 @@
           <t>Financial Assets</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>1261</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>995</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>372</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>450</v>
       </c>
     </row>
@@ -1687,16 +1684,16 @@
           <t>Investments And Advances</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>202</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>563</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>640</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>307</v>
       </c>
     </row>
@@ -1706,16 +1703,16 @@
           <t>Other Investments</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>82</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>112</v>
       </c>
     </row>
@@ -1725,16 +1722,16 @@
           <t>Investmentin Financial Assets</t>
         </is>
       </c>
-      <c r="C59" s="29" t="n">
+      <c r="C59" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="D59" s="29" t="n">
+      <c r="D59" s="25" t="n">
         <v>474</v>
       </c>
-      <c r="E59" s="29" t="n">
+      <c r="E59" s="25" t="n">
         <v>538</v>
       </c>
-      <c r="F59" s="29" t="n">
+      <c r="F59" s="25" t="n">
         <v>192</v>
       </c>
     </row>
@@ -1744,16 +1741,16 @@
           <t>Available For Sale Securities</t>
         </is>
       </c>
-      <c r="C60" s="29" t="n">
+      <c r="C60" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="D60" s="29" t="n">
+      <c r="D60" s="25" t="n">
         <v>474</v>
       </c>
-      <c r="E60" s="29" t="n">
+      <c r="E60" s="25" t="n">
         <v>538</v>
       </c>
-      <c r="F60" s="29" t="n">
+      <c r="F60" s="25" t="n">
         <v>192</v>
       </c>
     </row>
@@ -1763,16 +1760,16 @@
           <t>Long Term Equity Investment</t>
         </is>
       </c>
-      <c r="C61" s="29" t="n">
+      <c r="C61" s="25" t="n">
         <v>82</v>
       </c>
-      <c r="D61" s="29" t="n">
+      <c r="D61" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="E61" s="29" t="n">
+      <c r="E61" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="29" t="n">
+      <c r="F61" s="25" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1782,16 +1779,16 @@
           <t>Goodwill And Other Intangible Assets</t>
         </is>
       </c>
-      <c r="C62" s="29" t="n">
+      <c r="C62" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="D62" s="29" t="n">
+      <c r="D62" s="25" t="n">
         <v>425</v>
       </c>
-      <c r="E62" s="29" t="n">
+      <c r="E62" s="25" t="n">
         <v>420</v>
       </c>
-      <c r="F62" s="29" t="n">
+      <c r="F62" s="25" t="n">
         <v>420</v>
       </c>
     </row>
@@ -1801,16 +1798,16 @@
           <t>Goodwill</t>
         </is>
       </c>
-      <c r="C63" s="29" t="n">
+      <c r="C63" s="25" t="n">
         <v>47</v>
       </c>
-      <c r="D63" s="29" t="n">
+      <c r="D63" s="25" t="n">
         <v>425</v>
       </c>
-      <c r="E63" s="29" t="n">
+      <c r="E63" s="25" t="n">
         <v>420</v>
       </c>
-      <c r="F63" s="29" t="n">
+      <c r="F63" s="25" t="n">
         <v>420</v>
       </c>
     </row>
@@ -1820,16 +1817,16 @@
           <t>Net PPE</t>
         </is>
       </c>
-      <c r="C64" s="29" t="n">
+      <c r="C64" s="25" t="n">
         <v>19822</v>
       </c>
-      <c r="D64" s="29" t="n">
+      <c r="D64" s="25" t="n">
         <v>22116</v>
       </c>
-      <c r="E64" s="29" t="n">
+      <c r="E64" s="25" t="n">
         <v>21235</v>
       </c>
-      <c r="F64" s="29" t="n">
+      <c r="F64" s="25" t="n">
         <v>22474</v>
       </c>
     </row>
@@ -1839,16 +1836,16 @@
           <t>Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="C65" s="29" t="n">
+      <c r="C65" s="25" t="n">
         <v>-16726</v>
       </c>
-      <c r="D65" s="29" t="n">
+      <c r="D65" s="25" t="n">
         <v>-17423</v>
       </c>
-      <c r="E65" s="29" t="n">
+      <c r="E65" s="25" t="n">
         <v>-18088</v>
       </c>
-      <c r="F65" s="29" t="n">
+      <c r="F65" s="25" t="n">
         <v>-19072</v>
       </c>
     </row>
@@ -1858,16 +1855,16 @@
           <t>Gross PPE</t>
         </is>
       </c>
-      <c r="C66" s="29" t="n">
+      <c r="C66" s="25" t="n">
         <v>36548</v>
       </c>
-      <c r="D66" s="29" t="n">
+      <c r="D66" s="25" t="n">
         <v>39539</v>
       </c>
-      <c r="E66" s="29" t="n">
+      <c r="E66" s="25" t="n">
         <v>39323</v>
       </c>
-      <c r="F66" s="29" t="n">
+      <c r="F66" s="25" t="n">
         <v>41546</v>
       </c>
     </row>
@@ -1877,16 +1874,16 @@
           <t>Construction In Progress</t>
         </is>
       </c>
-      <c r="C67" s="29" t="n">
+      <c r="C67" s="25" t="n">
         <v>630</v>
       </c>
-      <c r="D67" s="29" t="n">
+      <c r="D67" s="25" t="n">
         <v>1133</v>
       </c>
-      <c r="E67" s="29" t="n">
+      <c r="E67" s="25" t="n">
         <v>1273</v>
       </c>
-      <c r="F67" s="29" t="n">
+      <c r="F67" s="25" t="n">
         <v>1995</v>
       </c>
     </row>
@@ -1896,16 +1893,16 @@
           <t>Other Properties</t>
         </is>
       </c>
-      <c r="B68" s="29" t="n">
+      <c r="B68" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="C68" s="29" t="n">
+      <c r="C68" s="25" t="n">
         <v>8</v>
       </c>
-      <c r="D68" s="29" t="n">
+      <c r="D68" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="E68" s="29" t="n">
+      <c r="E68" s="25" t="n">
         <v>15</v>
       </c>
     </row>
@@ -1915,16 +1912,16 @@
           <t>Properties</t>
         </is>
       </c>
-      <c r="B69" s="29" t="n">
+      <c r="B69" s="25" t="n">
         <v>35076</v>
       </c>
-      <c r="C69" s="29" t="n">
+      <c r="C69" s="25" t="n">
         <v>35910</v>
       </c>
-      <c r="D69" s="29" t="n">
+      <c r="D69" s="25" t="n">
         <v>38392</v>
       </c>
-      <c r="E69" s="29" t="n">
+      <c r="E69" s="25" t="n">
         <v>38035</v>
       </c>
     </row>
@@ -1934,16 +1931,16 @@
           <t>Current Assets</t>
         </is>
       </c>
-      <c r="C70" s="29" t="n">
+      <c r="C70" s="25" t="n">
         <v>9360</v>
       </c>
-      <c r="D70" s="29" t="n">
+      <c r="D70" s="25" t="n">
         <v>8299</v>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="25" t="n">
         <v>10776</v>
       </c>
-      <c r="F70" s="29" t="n">
+      <c r="F70" s="25" t="n">
         <v>12119</v>
       </c>
     </row>
@@ -1953,16 +1950,16 @@
           <t>Other Current Assets</t>
         </is>
       </c>
-      <c r="C71" s="29" t="n">
+      <c r="C71" s="25" t="n">
         <v>1643</v>
       </c>
-      <c r="D71" s="29" t="n">
+      <c r="D71" s="25" t="n">
         <v>2315</v>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="25" t="n">
         <v>1486</v>
       </c>
-      <c r="F71" s="29" t="n">
+      <c r="F71" s="25" t="n">
         <v>1424</v>
       </c>
     </row>
@@ -1972,16 +1969,16 @@
           <t>Hedging Assets Current</t>
         </is>
       </c>
-      <c r="C72" s="29" t="n">
+      <c r="C72" s="25" t="n">
         <v>2368</v>
       </c>
-      <c r="D72" s="29" t="n">
+      <c r="D72" s="25" t="n">
         <v>1179</v>
       </c>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="25" t="n">
         <v>843</v>
       </c>
-      <c r="F72" s="29" t="n">
+      <c r="F72" s="25" t="n">
         <v>945</v>
       </c>
     </row>
@@ -1991,7 +1988,7 @@
           <t>Assets Held For Sale Current</t>
         </is>
       </c>
-      <c r="B73" s="29" t="n">
+      <c r="B73" s="25" t="n">
         <v>13</v>
       </c>
     </row>
@@ -2001,16 +1998,16 @@
           <t>Restricted Cash</t>
         </is>
       </c>
-      <c r="C74" s="29" t="n">
+      <c r="C74" s="25" t="n">
         <v>106</v>
       </c>
-      <c r="D74" s="29" t="n">
+      <c r="D74" s="25" t="n">
         <v>86</v>
       </c>
-      <c r="E74" s="29" t="n">
+      <c r="E74" s="25" t="n">
         <v>107</v>
       </c>
-      <c r="F74" s="29" t="n">
+      <c r="F74" s="25" t="n">
         <v>107</v>
       </c>
     </row>
@@ -2020,16 +2017,16 @@
           <t>Inventory</t>
         </is>
       </c>
-      <c r="C75" s="29" t="n">
+      <c r="C75" s="25" t="n">
         <v>1505</v>
       </c>
-      <c r="D75" s="29" t="n">
+      <c r="D75" s="25" t="n">
         <v>1500</v>
       </c>
-      <c r="E75" s="29" t="n">
+      <c r="E75" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="F75" s="29" t="n">
+      <c r="F75" s="25" t="n">
         <v>1736</v>
       </c>
     </row>
@@ -2039,16 +2036,16 @@
           <t>Raw Materials</t>
         </is>
       </c>
-      <c r="B76" s="29" t="n">
+      <c r="B76" s="25" t="n">
         <v>1288</v>
       </c>
-      <c r="C76" s="29" t="n">
+      <c r="C76" s="25" t="n">
         <v>1505</v>
       </c>
-      <c r="D76" s="29" t="n">
+      <c r="D76" s="25" t="n">
         <v>1500</v>
       </c>
-      <c r="E76" s="29" t="n">
+      <c r="E76" s="25" t="n">
         <v>1600</v>
       </c>
     </row>
@@ -2058,16 +2055,16 @@
           <t>Receivables</t>
         </is>
       </c>
-      <c r="C77" s="29" t="n">
+      <c r="C77" s="25" t="n">
         <v>3316</v>
       </c>
-      <c r="D77" s="29" t="n">
+      <c r="D77" s="25" t="n">
         <v>2851</v>
       </c>
-      <c r="E77" s="29" t="n">
+      <c r="E77" s="25" t="n">
         <v>3718</v>
       </c>
-      <c r="F77" s="29" t="n">
+      <c r="F77" s="25" t="n">
         <v>4266</v>
       </c>
     </row>
@@ -2077,16 +2074,16 @@
           <t>Other Receivables</t>
         </is>
       </c>
-      <c r="C78" s="29" t="n">
+      <c r="C78" s="25" t="n">
         <v>731</v>
       </c>
-      <c r="D78" s="29" t="n">
+      <c r="D78" s="25" t="n">
         <v>917</v>
       </c>
-      <c r="E78" s="29" t="n">
+      <c r="E78" s="25" t="n">
         <v>602</v>
       </c>
-      <c r="F78" s="29" t="n">
+      <c r="F78" s="25" t="n">
         <v>689</v>
       </c>
     </row>
@@ -2096,10 +2093,10 @@
           <t>Duefrom Related Parties Current</t>
         </is>
       </c>
-      <c r="B79" s="29" t="n">
+      <c r="B79" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="C79" s="29" t="n">
+      <c r="C79" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2109,16 +2106,16 @@
           <t>Accounts Receivable</t>
         </is>
       </c>
-      <c r="C80" s="29" t="n">
+      <c r="C80" s="25" t="n">
         <v>2585</v>
       </c>
-      <c r="D80" s="29" t="n">
+      <c r="D80" s="25" t="n">
         <v>1934</v>
       </c>
-      <c r="E80" s="29" t="n">
+      <c r="E80" s="25" t="n">
         <v>3116</v>
       </c>
-      <c r="F80" s="29" t="n">
+      <c r="F80" s="25" t="n">
         <v>3577</v>
       </c>
     </row>
@@ -2128,16 +2125,16 @@
           <t>Allowance For Doubtful Accounts Receivable</t>
         </is>
       </c>
-      <c r="C81" s="29" t="n">
+      <c r="C81" s="25" t="n">
         <v>-46</v>
       </c>
-      <c r="D81" s="29" t="n">
+      <c r="D81" s="25" t="n">
         <v>-56</v>
       </c>
-      <c r="E81" s="29" t="n">
+      <c r="E81" s="25" t="n">
         <v>-190</v>
       </c>
-      <c r="F81" s="29" t="n">
+      <c r="F81" s="25" t="n">
         <v>-158</v>
       </c>
     </row>
@@ -2147,16 +2144,16 @@
           <t>Gross Accounts Receivable</t>
         </is>
       </c>
-      <c r="C82" s="29" t="n">
+      <c r="C82" s="25" t="n">
         <v>2631</v>
       </c>
-      <c r="D82" s="29" t="n">
+      <c r="D82" s="25" t="n">
         <v>1990</v>
       </c>
-      <c r="E82" s="29" t="n">
+      <c r="E82" s="25" t="n">
         <v>3306</v>
       </c>
-      <c r="F82" s="29" t="n">
+      <c r="F82" s="25" t="n">
         <v>3735</v>
       </c>
     </row>
@@ -2166,16 +2163,16 @@
           <t>Cash Cash Equivalents And Short Term Investments</t>
         </is>
       </c>
-      <c r="C83" s="29" t="n">
+      <c r="C83" s="25" t="n">
         <v>422</v>
       </c>
-      <c r="D83" s="29" t="n">
+      <c r="D83" s="25" t="n">
         <v>368</v>
       </c>
-      <c r="E83" s="29" t="n">
+      <c r="E83" s="25" t="n">
         <v>3022</v>
       </c>
-      <c r="F83" s="29" t="n">
+      <c r="F83" s="25" t="n">
         <v>3641</v>
       </c>
     </row>
@@ -2185,16 +2182,16 @@
           <t>Cash And Cash Equivalents</t>
         </is>
       </c>
-      <c r="C84" s="29" t="n">
+      <c r="C84" s="25" t="n">
         <v>422</v>
       </c>
-      <c r="D84" s="29" t="n">
+      <c r="D84" s="25" t="n">
         <v>368</v>
       </c>
-      <c r="E84" s="29" t="n">
+      <c r="E84" s="25" t="n">
         <v>3022</v>
       </c>
-      <c r="F84" s="29" t="n">
+      <c r="F84" s="25" t="n">
         <v>3641</v>
       </c>
     </row>
@@ -2230,7 +2227,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -2272,16 +2269,16 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-4042</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>-7723</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>-5029</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>1288</v>
       </c>
     </row>
@@ -2291,16 +2288,16 @@
           <t>Repurchase Of Capital Stock</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="29" t="n">
+      <c r="D6" s="25" t="n">
         <v>-992</v>
       </c>
-      <c r="E6" s="29" t="n">
+      <c r="E6" s="25" t="n">
         <v>-999</v>
       </c>
-      <c r="F6" s="29" t="n">
+      <c r="F6" s="25" t="n">
         <v>-400</v>
       </c>
     </row>
@@ -2310,16 +2307,16 @@
           <t>Repayment Of Debt</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>-2600</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>-368</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>-1965</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>-1076</v>
       </c>
     </row>
@@ -2329,16 +2326,16 @@
           <t>Issuance Of Debt</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>271</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>3880</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>1120</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -2348,16 +2345,16 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-1689</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>-2422</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>-2565</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>-2949</v>
       </c>
     </row>
@@ -2367,16 +2364,16 @@
           <t>Interest Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>264</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>375</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>412</v>
       </c>
     </row>
@@ -2386,16 +2383,16 @@
           <t>Income Tax Paid Supplemental Data</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>287</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>466</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>436</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>446</v>
       </c>
     </row>
@@ -2405,16 +2402,16 @@
           <t>End Cash Position</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>528</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>454</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>3129</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>3748</v>
       </c>
     </row>
@@ -2424,16 +2421,16 @@
           <t>Beginning Cash Position</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>576</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>528</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>454</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>3129</v>
       </c>
     </row>
@@ -2443,16 +2440,16 @@
           <t>Changes In Cash</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>-48</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>-74</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>2675</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>619</v>
       </c>
     </row>
@@ -2462,16 +2459,16 @@
           <t>Financing Cash Flow</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-799</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>2196</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>-2289</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>-420</v>
       </c>
     </row>
@@ -2481,16 +2478,16 @@
           <t>Cash Flow From Continuing Financing Activities</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>-799</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>2196</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>-2289</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>-420</v>
       </c>
     </row>
@@ -2500,16 +2497,16 @@
           <t>Net Other Financing Charges</t>
         </is>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>1715</v>
       </c>
-      <c r="D17" s="29" t="n">
+      <c r="D17" s="25" t="n">
         <v>42</v>
       </c>
-      <c r="E17" s="29" t="n">
+      <c r="E17" s="25" t="n">
         <v>-1</v>
       </c>
-      <c r="F17" s="29" t="n">
+      <c r="F17" s="25" t="n">
         <v>-108</v>
       </c>
     </row>
@@ -2519,16 +2516,16 @@
           <t>Cash Dividends Paid</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-185</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>-366</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>-444</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>-486</v>
       </c>
     </row>
@@ -2538,16 +2535,16 @@
           <t>Common Stock Dividend Paid</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-185</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>-366</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>-444</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>-486</v>
       </c>
     </row>
@@ -2557,16 +2554,16 @@
           <t>Net Common Stock Issuance</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>-992</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>-999</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>-400</v>
       </c>
     </row>
@@ -2576,16 +2573,16 @@
           <t>Common Stock Payments</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>-992</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>-999</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>-400</v>
       </c>
     </row>
@@ -2595,16 +2592,16 @@
           <t>Net Issuance Payments Of Debt</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>-2329</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>3512</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>-845</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>574</v>
       </c>
     </row>
@@ -2614,16 +2611,16 @@
           <t>Net Short Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>-923</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>485</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>-1644</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -2633,16 +2630,16 @@
           <t>Short Term Debt Payments</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
+      <c r="C24" s="25" t="n">
         <v>-1180</v>
       </c>
-      <c r="D24" s="29" t="n">
+      <c r="D24" s="25" t="n">
         <v>-200</v>
       </c>
-      <c r="E24" s="29" t="n">
+      <c r="E24" s="25" t="n">
         <v>-1844</v>
       </c>
-      <c r="F24" s="29" t="n">
+      <c r="F24" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2652,16 +2649,16 @@
           <t>Short Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
+      <c r="C25" s="25" t="n">
         <v>257</v>
       </c>
-      <c r="D25" s="29" t="n">
+      <c r="D25" s="25" t="n">
         <v>685</v>
       </c>
-      <c r="E25" s="29" t="n">
+      <c r="E25" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="F25" s="29" t="n">
+      <c r="F25" s="25" t="n">
         <v>1650</v>
       </c>
     </row>
@@ -2671,16 +2668,16 @@
           <t>Net Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>-1406</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>3027</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>799</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>-1076</v>
       </c>
     </row>
@@ -2690,16 +2687,16 @@
           <t>Long Term Debt Payments</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>-1420</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>-168</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>-121</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>-1076</v>
       </c>
     </row>
@@ -2709,16 +2706,16 @@
           <t>Long Term Debt Issuance</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>3195</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>920</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2728,16 +2725,16 @@
           <t>Investing Cash Flow</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>3104</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>3031</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>7428</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>-3198</v>
       </c>
     </row>
@@ -2747,16 +2744,16 @@
           <t>Cash Flow From Continuing Investing Activities</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>3104</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>3031</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>7428</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>-3198</v>
       </c>
     </row>
@@ -2766,16 +2763,16 @@
           <t>Net Other Investing Changes</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>5014</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>5681</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>10270</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>89</v>
       </c>
     </row>
@@ -2785,16 +2782,16 @@
           <t>Net Investment Purchase And Sale</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>-221</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-228</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>-277</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>-338</v>
       </c>
     </row>
@@ -2804,16 +2801,16 @@
           <t>Sale Of Investment</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>4050</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>5822</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>6005</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>6946</v>
       </c>
     </row>
@@ -2823,16 +2820,16 @@
           <t>Purchase Of Investment</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>-4271</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>-6050</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>-6282</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>-7284</v>
       </c>
     </row>
@@ -2842,16 +2839,16 @@
           <t>Capital Expenditure Reported</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>-1689</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>-2422</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>-2565</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>-2949</v>
       </c>
     </row>
@@ -2861,16 +2858,16 @@
           <t>Operating Cash Flow</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>-2353</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>-5301</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>-2464</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>4237</v>
       </c>
     </row>
@@ -2880,16 +2877,16 @@
           <t>Cash Flow From Continuing Operating Activities</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>-2353</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>-5301</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>-2464</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>4237</v>
       </c>
     </row>
@@ -2899,16 +2896,16 @@
           <t>Change In Working Capital</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>-5246</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>-8355</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>-9168</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>-7</v>
       </c>
     </row>
@@ -2918,16 +2915,16 @@
           <t>Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>-5292</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>-7481</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>-10878</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>174</v>
       </c>
     </row>
@@ -2937,16 +2934,16 @@
           <t>Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>1142</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>-1330</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>1121</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>316</v>
       </c>
     </row>
@@ -2956,7 +2953,7 @@
           <t>Change In Payable</t>
         </is>
       </c>
-      <c r="B41" s="29" t="n">
+      <c r="B41" s="25" t="n">
         <v>346</v>
       </c>
     </row>
@@ -2966,7 +2963,7 @@
           <t>Change In Account Payable</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="25" t="n">
         <v>346</v>
       </c>
     </row>
@@ -2976,16 +2973,16 @@
           <t>Change In Inventory</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-228</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>-99</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>-134</v>
       </c>
     </row>
@@ -2995,16 +2992,16 @@
           <t>Change In Receivables</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>-868</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>396</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>688</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>-363</v>
       </c>
     </row>
@@ -3014,16 +3011,16 @@
           <t>Changes In Account Receivables</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>-868</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>396</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>688</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>-363</v>
       </c>
     </row>
@@ -3033,16 +3030,16 @@
           <t>Other Non Cash Items</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>61</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>-870</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>2356</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>-505</v>
       </c>
     </row>
@@ -3052,7 +3049,7 @@
           <t>Unrealized Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="B47" s="29" t="n">
+      <c r="B47" s="25" t="n">
         <v>160</v>
       </c>
     </row>
@@ -3062,10 +3059,10 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n">
+      <c r="B48" s="25" t="n">
         <v>545</v>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3075,16 +3072,16 @@
           <t>Deferred Tax</t>
         </is>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>-643</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>251</v>
       </c>
-      <c r="E49" s="29" t="n">
+      <c r="E49" s="25" t="n">
         <v>222</v>
       </c>
-      <c r="F49" s="29" t="n">
+      <c r="F49" s="25" t="n">
         <v>273</v>
       </c>
     </row>
@@ -3094,16 +3091,16 @@
           <t>Deferred Income Tax</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>-643</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>251</v>
       </c>
-      <c r="E50" s="29" t="n">
+      <c r="E50" s="25" t="n">
         <v>222</v>
       </c>
-      <c r="F50" s="29" t="n">
+      <c r="F50" s="25" t="n">
         <v>273</v>
       </c>
     </row>
@@ -3113,16 +3110,16 @@
           <t>Depreciation Amortization Depletion</t>
         </is>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>1849</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>1883</v>
       </c>
-      <c r="E51" s="29" t="n">
+      <c r="E51" s="25" t="n">
         <v>2007</v>
       </c>
-      <c r="F51" s="29" t="n">
+      <c r="F51" s="25" t="n">
         <v>1937</v>
       </c>
     </row>
@@ -3132,16 +3129,16 @@
           <t>Depreciation And Amortization</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>1849</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>1883</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>2007</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>1937</v>
       </c>
     </row>
@@ -3151,16 +3148,16 @@
           <t>Amortization Cash Flow</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3170,16 +3167,16 @@
           <t>Amortization Of Intangibles</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>18</v>
       </c>
     </row>
@@ -3189,16 +3186,16 @@
           <t>Depreciation</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>1823</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>1860</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>1985</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>1919</v>
       </c>
     </row>
@@ -3208,16 +3205,16 @@
           <t>Operating Gains Losses</t>
         </is>
       </c>
-      <c r="C56" s="29" t="n">
+      <c r="C56" s="25" t="n">
         <v>1793</v>
       </c>
-      <c r="D56" s="29" t="n">
+      <c r="D56" s="25" t="n">
         <v>213</v>
       </c>
-      <c r="E56" s="29" t="n">
+      <c r="E56" s="25" t="n">
         <v>-1619</v>
       </c>
-      <c r="F56" s="29" t="n">
+      <c r="F56" s="25" t="n">
         <v>216</v>
       </c>
     </row>
@@ -3227,16 +3224,16 @@
           <t>Gain Loss On Investment Securities</t>
         </is>
       </c>
-      <c r="C57" s="29" t="n">
+      <c r="C57" s="25" t="n">
         <v>1793</v>
       </c>
-      <c r="D57" s="29" t="n">
+      <c r="D57" s="25" t="n">
         <v>213</v>
       </c>
-      <c r="E57" s="29" t="n">
+      <c r="E57" s="25" t="n">
         <v>-1619</v>
       </c>
-      <c r="F57" s="29" t="n">
+      <c r="F57" s="25" t="n">
         <v>216</v>
       </c>
     </row>
@@ -3246,16 +3243,16 @@
           <t>Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="C58" s="29" t="n">
+      <c r="C58" s="25" t="n">
         <v>-167</v>
       </c>
-      <c r="D58" s="29" t="n">
+      <c r="D58" s="25" t="n">
         <v>1577</v>
       </c>
-      <c r="E58" s="29" t="n">
+      <c r="E58" s="25" t="n">
         <v>3738</v>
       </c>
-      <c r="F58" s="29" t="n">
+      <c r="F58" s="25" t="n">
         <v>2323</v>
       </c>
     </row>
@@ -3265,6 +3262,285 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CEG — 12-month price target (lens triangulation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Blue = inputs (weights, Ke, dividends, Street weight); black = live formulas. Change a weight and the blended fair value and target recalculate. Guardrail exclusions are already reflected in the effective weights.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Lens</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Value / share</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
+        <is>
+          <t>Weight</t>
+        </is>
+      </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Discounted cash flow (FCFF)</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>intrinsic</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>282.7568220272482</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>231.7571806850097</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>340.6284356626006</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Forward P/E</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>208.9017763350946</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>171.2994565947775</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>246.5040960754116</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.3333333333333334</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Forward EV/EBITDA</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>relative</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>233.7981950244186</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>188.8479441202007</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>278.7484459286364</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Weights sum</t>
+        </is>
+      </c>
+      <c r="B9" s="12">
+        <f>SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Blended fair value (today)</t>
+        </is>
+      </c>
+      <c r="B10" s="14">
+        <f>SUMPRODUCT(C5:C7,F5:F7)/SUM(F5:F7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Cost of equity (Ke)</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n">
+        <v>0.08636605555468493</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Dividends per share (12m)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1.361</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Model 12-month target = FV×(1+Ke)−DPS</t>
+        </is>
+      </c>
+      <c r="B13" s="16">
+        <f>$B$10*(1+$B$11)-$B$12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Street mean target</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>357.81</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Street weight in target</t>
+        </is>
+      </c>
+      <c r="B15" s="11" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Published 12-month target</t>
+        </is>
+      </c>
+      <c r="B16" s="17">
+        <f>(1-$B$15)*$B$13+$B$15*$B$14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Current price</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>244.52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Engine target (incl. plausibility band)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>278.3245544984664</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Guardrails</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Target anchored 15% to the Street consensus ($357.81); model-only target $264.30.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3289,14 +3565,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CEG — projected P&amp;L &amp; levered FCF (analyst-driven)</t>
+          <t>CEG — projected P&amp;L &amp; levered FCF (DCF base case)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue = analyst estimates; black = live formulas. The Levered FCF row is the exact cash flow discounted on the 'SWS Valuation' sheet — P&amp;L, cash flow and fair value are one reconciled chain.</t>
+          <t>Blue = consensus-sourced figures; black = live formulas. Revenue and EBIT margin are the DCF base-case drivers; levered FCF = unlevered FCF less after-tax interest.</t>
         </is>
       </c>
     </row>
@@ -3358,40 +3634,40 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="11" t="inlineStr">
+      <c r="A5" s="13" t="inlineStr">
         <is>
           <t>Revenue (mn)</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
-        <v>35617.88948</v>
-      </c>
-      <c r="C5" s="13" t="n">
-        <v>36686.4261644</v>
-      </c>
-      <c r="D5" s="13" t="n">
-        <v>37787.018949332</v>
-      </c>
-      <c r="E5" s="13" t="n">
-        <v>38920.62951781196</v>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>40088.24840334632</v>
-      </c>
-      <c r="G5" s="13" t="n">
-        <v>41290.89585544671</v>
-      </c>
-      <c r="H5" s="13" t="n">
-        <v>42529.62273111011</v>
-      </c>
-      <c r="I5" s="13" t="n">
-        <v>43805.51141304341</v>
-      </c>
-      <c r="J5" s="13" t="n">
-        <v>45119.67675543472</v>
-      </c>
-      <c r="K5" s="13" t="n">
-        <v>46473.26705809776</v>
+      <c r="B5" s="18" t="n">
+        <v>35620</v>
+      </c>
+      <c r="C5" s="19" t="n">
+        <v>41489.81542106217</v>
+      </c>
+      <c r="D5" s="19" t="n">
+        <v>46684.81047221891</v>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>51205.70282363475</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>55122.88947284904</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>58535.99793296073</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>61548.58653522813</v>
+      </c>
+      <c r="I5" s="19" t="n">
+        <v>64255.02592469643</v>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>66735.31941725372</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>68403.70240268506</v>
       </c>
     </row>
     <row r="6">
@@ -3405,39 +3681,39 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="12">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="12">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="14">
+      <c r="E6" s="12">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
         <v/>
       </c>
-      <c r="K6" s="14">
+      <c r="K6" s="12">
         <f>K5/J5-1</f>
         <v/>
       </c>
@@ -3448,35 +3724,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="C7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="D7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="I7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.1644146790428073</v>
+      <c r="B7" s="11" t="n">
+        <v>0.2052475596989307</v>
+      </c>
+      <c r="C7" s="11" t="n">
+        <v>0.2012638513087025</v>
+      </c>
+      <c r="D7" s="11" t="n">
+        <v>0.1972801429184742</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.193296434528246</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.1893127261380177</v>
+      </c>
+      <c r="G7" s="11" t="n">
+        <v>0.1853290177477895</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.1813453093575612</v>
+      </c>
+      <c r="I7" s="11" t="n">
+        <v>0.1773616009673329</v>
+      </c>
+      <c r="J7" s="11" t="n">
+        <v>0.1773616009673329</v>
+      </c>
+      <c r="K7" s="11" t="n">
+        <v>0.1773616009673329</v>
       </c>
     </row>
     <row r="8">
@@ -3485,43 +3761,43 @@
           <t>EBIT (mn)</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
         <v/>
       </c>
-      <c r="G8" s="13">
+      <c r="G8" s="19">
         <f>G5*G7</f>
         <v/>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="19">
         <f>H5*H7</f>
         <v/>
       </c>
-      <c r="I8" s="13">
+      <c r="I8" s="19">
         <f>I5*I7</f>
         <v/>
       </c>
-      <c r="J8" s="13">
+      <c r="J8" s="19">
         <f>J5*J7</f>
         <v/>
       </c>
-      <c r="K8" s="13">
+      <c r="K8" s="19">
         <f>K5*K7</f>
         <v/>
       </c>
@@ -3532,35 +3808,35 @@
           <t>Net income (mn)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
-        <v>4850.52740997151</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <v>3331.994762669628</v>
-      </c>
-      <c r="D9" s="13" t="n">
-        <v>3431.954605549717</v>
-      </c>
-      <c r="E9" s="13" t="n">
-        <v>3534.913243716208</v>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>3640.960641027694</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <v>3750.189460258525</v>
-      </c>
-      <c r="H9" s="13" t="n">
-        <v>3862.695144066281</v>
-      </c>
-      <c r="I9" s="13" t="n">
-        <v>3978.575998388269</v>
-      </c>
-      <c r="J9" s="13" t="n">
-        <v>4097.933278339917</v>
-      </c>
-      <c r="K9" s="13" t="n">
-        <v>4220.871276690114</v>
+      <c r="B9" s="18" t="n">
+        <v>4849.44539086</v>
+      </c>
+      <c r="C9" s="19" t="n">
+        <v>5590.764766857072</v>
+      </c>
+      <c r="D9" s="19" t="n">
+        <v>6203.789146643189</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>6694.369018542216</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>7077.754170234815</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>7372.257776958407</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>7595.569202017806</v>
+      </c>
+      <c r="I9" s="19" t="n">
+        <v>7763.038830619873</v>
+      </c>
+      <c r="J9" s="19" t="n">
+        <v>8076.765231201512</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>8287.795010694002</v>
       </c>
     </row>
     <row r="10">
@@ -3611,40 +3887,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr">
         <is>
           <t>Levered FCF (mn)</t>
         </is>
       </c>
-      <c r="B12" s="17" t="n">
-        <v>2694.040234602546</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <v>2788.331642813635</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>2885.923250312112</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>2986.930564073036</v>
-      </c>
-      <c r="F12" s="17" t="n">
-        <v>3091.473133815592</v>
-      </c>
-      <c r="G12" s="17" t="n">
-        <v>3199.674693499138</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>3311.663307771607</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>3427.571523543613</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>3547.53652686764</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>3671.700305308007</v>
+      <c r="B12" s="20" t="n">
+        <v>4115.400504666752</v>
+      </c>
+      <c r="C12" s="20" t="n">
+        <v>4811.06573334487</v>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>5392.656677636085</v>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>5875.97646236353</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>6272.366069495353</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>6596.361548848513</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>6862.441300134499</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>7083.430048819514</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>7459.544752551667</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>7747.887269074251</v>
       </c>
     </row>
     <row r="13">
@@ -3653,43 +3929,43 @@
           <t>FCF margin</t>
         </is>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="12">
         <f>B12/B5</f>
         <v/>
       </c>
-      <c r="C13" s="14">
+      <c r="C13" s="12">
         <f>C12/C5</f>
         <v/>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="12">
         <f>D12/D5</f>
         <v/>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="12">
         <f>E12/E5</f>
         <v/>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <f>F12/F5</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="12">
         <f>G12/G5</f>
         <v/>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="12">
         <f>H12/H5</f>
         <v/>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="12">
         <f>I12/I5</f>
         <v/>
       </c>
-      <c r="J13" s="14">
+      <c r="J13" s="12">
         <f>J12/J5</f>
         <v/>
       </c>
-      <c r="K13" s="14">
+      <c r="K13" s="12">
         <f>K12/K5</f>
         <v/>
       </c>
@@ -3697,438 +3973,8 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>→ These Levered FCF figures feed the DCF on the 'SWS Valuation' sheet.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E34"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>CEG — 2-Stage Free Cash Flow to Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Simply Wall St methodology. Blue = analyst inputs you can change; black = live formulas. Discounted at the cost of equity. Every figure is traceable; change a blue cell and the model recalculates.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>Cost of equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Risk-free rate</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>0.036</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>Equity risk premium</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>0.046</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Levered beta (clamped 0.8–2.0)</t>
-        </is>
-      </c>
-      <c r="B7" s="19" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Cost of equity = Rf + β·ERP</t>
-        </is>
-      </c>
-      <c r="B8" s="20">
-        <f>$B$5+$B$7*$B$6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Perpetual growth (g)</t>
-        </is>
-      </c>
-      <c r="B10" s="18" t="n">
-        <v>0.025</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>Shares outstanding (mn)</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>357.102017</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>Stage 1 — 10-year cash-flow forecast</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>Year</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>Cash flow (mn)</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>Source</t>
-        </is>
-      </c>
-      <c r="D14" s="10" t="inlineStr">
-        <is>
-          <t>Discount factor</t>
-        </is>
-      </c>
-      <c r="E14" s="10" t="inlineStr">
-        <is>
-          <t>PV (mn)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="n">
-        <v>2026</v>
-      </c>
-      <c r="B15" s="12" t="n">
-        <v>2694.040234602546</v>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D15" s="22">
-        <f>1/(1+$B$8)^1</f>
-        <v/>
-      </c>
-      <c r="E15" s="13">
-        <f>B15*D15</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>2027</v>
-      </c>
-      <c r="B16" s="12" t="n">
-        <v>2788.331642813635</v>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D16" s="22">
-        <f>1/(1+$B$8)^2</f>
-        <v/>
-      </c>
-      <c r="E16" s="13">
-        <f>B16*D16</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>2028</v>
-      </c>
-      <c r="B17" s="12" t="n">
-        <v>2885.923250312112</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D17" s="22">
-        <f>1/(1+$B$8)^3</f>
-        <v/>
-      </c>
-      <c r="E17" s="13">
-        <f>B17*D17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>2029</v>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>2986.930564073036</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D18" s="22">
-        <f>1/(1+$B$8)^4</f>
-        <v/>
-      </c>
-      <c r="E18" s="13">
-        <f>B18*D18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>2030</v>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>3091.473133815592</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D19" s="22">
-        <f>1/(1+$B$8)^5</f>
-        <v/>
-      </c>
-      <c r="E19" s="13">
-        <f>B19*D19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>2031</v>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>3199.674693499138</v>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D20" s="22">
-        <f>1/(1+$B$8)^6</f>
-        <v/>
-      </c>
-      <c r="E20" s="13">
-        <f>B20*D20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="21" t="n">
-        <v>2032</v>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>3311.663307771607</v>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D21" s="22">
-        <f>1/(1+$B$8)^7</f>
-        <v/>
-      </c>
-      <c r="E21" s="13">
-        <f>B21*D21</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="21" t="n">
-        <v>2033</v>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>3427.571523543613</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D22" s="22">
-        <f>1/(1+$B$8)^8</f>
-        <v/>
-      </c>
-      <c r="E22" s="13">
-        <f>B22*D22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="21" t="n">
-        <v>2034</v>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>3547.53652686764</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D23" s="22">
-        <f>1/(1+$B$8)^9</f>
-        <v/>
-      </c>
-      <c r="E23" s="13">
-        <f>B23*D23</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="n">
-        <v>2035</v>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>3671.700305308007</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Analyst</t>
-        </is>
-      </c>
-      <c r="D24" s="22">
-        <f>1/(1+$B$8)^10</f>
-        <v/>
-      </c>
-      <c r="E24" s="13">
-        <f>B24*D24</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>PV of next 10 years' cash flows</t>
-        </is>
-      </c>
-      <c r="B25" s="23">
-        <f>SUM(E15:E24)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>Stage 2 — terminal value</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>Terminal value = CFn·(1+g)/(Ke−g)</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>B24*(1+$B$10)/($B$8-$B$10)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>PV of terminal value</t>
-        </is>
-      </c>
-      <c r="B29" s="13">
-        <f>$B$28/(1+$B$8)^10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
-        <is>
-          <t>Total equity value</t>
-        </is>
-      </c>
-      <c r="B31" s="23">
-        <f>$B$25+$B$29</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>Value per share</t>
-        </is>
-      </c>
-      <c r="B32" s="24">
-        <f>$B$31/$B$11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Current price</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n">
-        <v>244.52</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Upside / (downside)</t>
-        </is>
-      </c>
-      <c r="B34" s="14">
-        <f>B32/$B$33-1</f>
-        <v/>
+          <t>→ Unlevered FCF (before interest) is what the 'DCF' sheet discounts.</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -4142,7 +3988,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:K30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -4168,7 +4014,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Blue cells are inputs — change them and the whole model recalculates. Source: yfinance, retrieved 2026-07-08.</t>
+          <t>Blue cells are inputs — change them and the whole model recalculates. Source: Yahoo snapshot as of 2026-07-08, retrieved 2026-10-13.</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4041,7 @@
           <t>Diluted shares (mn)</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="18" t="n">
         <v>357.102017</v>
       </c>
     </row>
@@ -4205,7 +4051,7 @@
           <t>Total debt (USDmm)</t>
         </is>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="18" t="n">
         <v>8992</v>
       </c>
     </row>
@@ -4215,7 +4061,7 @@
           <t>Cash &amp; ST investments (USDmm)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
+      <c r="B8" s="18" t="n">
         <v>3641</v>
       </c>
     </row>
@@ -4225,7 +4071,7 @@
           <t>Minority interest (USDmm)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="18" t="n">
         <v>336</v>
       </c>
     </row>
@@ -4235,7 +4081,7 @@
           <t>Net debt (USDmm)</t>
         </is>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="19">
         <f>Assumptions!$B$7-Assumptions!$B$8</f>
         <v/>
       </c>
@@ -4253,7 +4099,7 @@
           <t>Risk-free rate (Rf)</t>
         </is>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="21" t="n">
         <v>0.043</v>
       </c>
     </row>
@@ -4263,7 +4109,7 @@
           <t>Equity risk premium (ERP)</t>
         </is>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="21" t="n">
         <v>0.046</v>
       </c>
     </row>
@@ -4273,7 +4119,7 @@
           <t>Country risk premium</t>
         </is>
       </c>
-      <c r="B15" s="18" t="n">
+      <c r="B15" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4283,7 +4129,7 @@
           <t>Size premium</t>
         </is>
       </c>
-      <c r="B16" s="18" t="n">
+      <c r="B16" s="15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4293,8 +4139,8 @@
           <t>Beta (levered)</t>
         </is>
       </c>
-      <c r="B17" s="26" t="n">
-        <v>1.12</v>
+      <c r="B17" s="22" t="n">
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -4303,7 +4149,7 @@
           <t>Pre-tax cost of debt</t>
         </is>
       </c>
-      <c r="B18" s="18" t="n">
+      <c r="B18" s="15" t="n">
         <v>0.051</v>
       </c>
     </row>
@@ -4313,7 +4159,7 @@
           <t>Tax rate</t>
         </is>
       </c>
-      <c r="B19" s="15" t="n">
+      <c r="B19" s="11" t="n">
         <v>0.286837674171915</v>
       </c>
     </row>
@@ -4330,7 +4176,7 @@
           <t>Terminal growth (g)</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="21" t="n">
         <v>0.025</v>
       </c>
     </row>
@@ -4372,6 +4218,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G25" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H25" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I25" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J25" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K25" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -4379,20 +4250,35 @@
           <t>Revenue growth</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v>0.01469039149633189</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>0.01594039149633189</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>0.01719039149633189</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>0.01844039149633189</v>
-      </c>
-      <c r="F26" s="15" t="n">
-        <v>0.01969039149633189</v>
+      <c r="B26" s="11" t="n">
+        <v>0.3950573767281558</v>
+      </c>
+      <c r="C26" s="11" t="n">
+        <v>0.1647898770651929</v>
+      </c>
+      <c r="D26" s="11" t="n">
+        <v>0.125211331948214</v>
+      </c>
+      <c r="E26" s="11" t="n">
+        <v>0.09683861422348755</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>0.07649903102992379</v>
+      </c>
+      <c r="G26" s="11" t="n">
+        <v>0.06191817034179282</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>0.05146557176180035</v>
+      </c>
+      <c r="I26" s="11" t="n">
+        <v>0.04397240524636979</v>
+      </c>
+      <c r="J26" s="11" t="n">
+        <v>0.03860077024113361</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.025</v>
       </c>
     </row>
     <row r="27">
@@ -4401,20 +4287,35 @@
           <t>EBIT margin</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v>0.1644146790428073</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>0.1592026475312204</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>0.1539906160196335</v>
-      </c>
-      <c r="E27" s="15" t="n">
-        <v>0.1487785845080466</v>
-      </c>
-      <c r="F27" s="15" t="n">
-        <v>0.1435665529964597</v>
+      <c r="B27" s="11" t="n">
+        <v>0.2052475596989307</v>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0.2012638513087025</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>0.1972801429184742</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>0.193296434528246</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>0.1893127261380177</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>0.1853290177477895</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>0.1813453093575612</v>
+      </c>
+      <c r="I27" s="11" t="n">
+        <v>0.1773616009673329</v>
+      </c>
+      <c r="J27" s="11" t="n">
+        <v>0.1773616009673329</v>
+      </c>
+      <c r="K27" s="11" t="n">
+        <v>0.1773616009673329</v>
       </c>
     </row>
     <row r="28">
@@ -4423,19 +4324,34 @@
           <t>D&amp;A % of revenue</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
+      <c r="B28" s="11" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="C28" s="15" t="n">
+      <c r="C28" s="11" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="D28" s="15" t="n">
+      <c r="D28" s="11" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="11" t="n">
         <v>0.07806074434667941</v>
       </c>
-      <c r="F28" s="15" t="n">
+      <c r="F28" s="11" t="n">
+        <v>0.07806074434667941</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>0.07806074434667941</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.07806074434667941</v>
+      </c>
+      <c r="I28" s="11" t="n">
+        <v>0.07806074434667941</v>
+      </c>
+      <c r="J28" s="11" t="n">
+        <v>0.07806074434667941</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.07806074434667941</v>
       </c>
     </row>
@@ -4445,20 +4361,35 @@
           <t>Capex % of revenue</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B29" s="11" t="n">
         <v>0.09765960882899036</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <v>0.09765960882899036</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0.09765960882899036</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>0.09765960882899036</v>
-      </c>
-      <c r="F29" s="15" t="n">
-        <v>0.09765960882899036</v>
+      <c r="C29" s="11" t="n">
+        <v>0.09634929882369669</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>0.09503898881840303</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0.09372867881310935</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0.09241836880781569</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0.09110805880252203</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0.08979774879722836</v>
+      </c>
+      <c r="I29" s="11" t="n">
+        <v>0.08848743879193469</v>
+      </c>
+      <c r="J29" s="11" t="n">
+        <v>0.08717712878664102</v>
+      </c>
+      <c r="K29" s="11" t="n">
+        <v>0.08586681878134736</v>
       </c>
     </row>
     <row r="30">
@@ -4467,7 +4398,7 @@
           <t>ΔNWC % of Δrevenue</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
+      <c r="B30" s="11" t="n">
         <v>0.00356234096692112</v>
       </c>
     </row>
@@ -4531,7 +4462,7 @@
           <t>Market value of equity (mm)</t>
         </is>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="23">
         <f>Assumptions!$B$5*Assumptions!$B$6</f>
         <v/>
       </c>
@@ -4542,7 +4473,7 @@
           <t>Debt (book, mm)</t>
         </is>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="23">
         <f>Assumptions!$B$7</f>
         <v/>
       </c>
@@ -4553,7 +4484,7 @@
           <t>Weight of equity</t>
         </is>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="12">
         <f>WACC!$B$6/(WACC!$B$6+WACC!$B$7)</f>
         <v/>
       </c>
@@ -4564,18 +4495,18 @@
           <t>Weight of debt</t>
         </is>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="12">
         <f>1-WACC!$B$8</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr">
         <is>
           <t>WACC</t>
         </is>
       </c>
-      <c r="B10" s="28">
+      <c r="B10" s="24">
         <f>WACC!$B$8*WACC!$B$4+WACC!$B$9*WACC!$B$5</f>
         <v/>
       </c>
@@ -4591,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -4604,6 +4535,11 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4671,6 +4607,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -4678,36 +4639,56 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B5" s="29" t="n">
+      <c r="B5" s="25" t="n">
         <v>24440</v>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>24918</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>23568</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>25533</v>
       </c>
-      <c r="F5" s="13">
+      <c r="F5" s="19">
         <f>E5*(1+Assumptions!B$26)</f>
         <v/>
       </c>
-      <c r="G5" s="13">
+      <c r="G5" s="19">
         <f>F5*(1+Assumptions!C$26)</f>
         <v/>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="19">
         <f>G5*(1+Assumptions!D$26)</f>
         <v/>
       </c>
-      <c r="I5" s="13">
+      <c r="I5" s="19">
         <f>H5*(1+Assumptions!E$26)</f>
         <v/>
       </c>
-      <c r="J5" s="13">
+      <c r="J5" s="19">
         <f>I5*(1+Assumptions!F$26)</f>
+        <v/>
+      </c>
+      <c r="K5" s="19">
+        <f>J5*(1+Assumptions!G$26)</f>
+        <v/>
+      </c>
+      <c r="L5" s="19">
+        <f>K5*(1+Assumptions!H$26)</f>
+        <v/>
+      </c>
+      <c r="M5" s="19">
+        <f>L5*(1+Assumptions!I$26)</f>
+        <v/>
+      </c>
+      <c r="N5" s="19">
+        <f>M5*(1+Assumptions!J$26)</f>
+        <v/>
+      </c>
+      <c r="O5" s="19">
+        <f>N5*(1+Assumptions!K$26)</f>
         <v/>
       </c>
     </row>
@@ -4717,36 +4698,56 @@
           <t xml:space="preserve">  growth %</t>
         </is>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="26">
         <f>C5/B5-1</f>
         <v/>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="26">
         <f>D5/C5-1</f>
         <v/>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="26">
         <f>E5/D5-1</f>
         <v/>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="12">
         <f>F5/E5-1</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="12">
         <f>G5/F5-1</f>
         <v/>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="12">
         <f>H5/G5-1</f>
         <v/>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="12">
         <f>I5/H5-1</f>
         <v/>
       </c>
-      <c r="J6" s="14">
+      <c r="J6" s="12">
         <f>J5/I5-1</f>
+        <v/>
+      </c>
+      <c r="K6" s="12">
+        <f>K5/J5-1</f>
+        <v/>
+      </c>
+      <c r="L6" s="12">
+        <f>L5/K5-1</f>
+        <v/>
+      </c>
+      <c r="M6" s="12">
+        <f>M5/L5-1</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>N5/M5-1</f>
+        <v/>
+      </c>
+      <c r="O6" s="12">
+        <f>O5/N5-1</f>
         <v/>
       </c>
     </row>
@@ -4756,36 +4757,56 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B7" s="29" t="n">
+      <c r="B7" s="25" t="n">
         <v>-408</v>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>2386</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>4848</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>4198</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="19">
         <f>F5*Assumptions!B$27</f>
         <v/>
       </c>
-      <c r="G7" s="13">
+      <c r="G7" s="19">
         <f>G5*Assumptions!C$27</f>
         <v/>
       </c>
-      <c r="H7" s="13">
+      <c r="H7" s="19">
         <f>H5*Assumptions!D$27</f>
         <v/>
       </c>
-      <c r="I7" s="13">
+      <c r="I7" s="19">
         <f>I5*Assumptions!E$27</f>
         <v/>
       </c>
-      <c r="J7" s="13">
+      <c r="J7" s="19">
         <f>J5*Assumptions!F$27</f>
+        <v/>
+      </c>
+      <c r="K7" s="19">
+        <f>K5*Assumptions!G$27</f>
+        <v/>
+      </c>
+      <c r="L7" s="19">
+        <f>L5*Assumptions!H$27</f>
+        <v/>
+      </c>
+      <c r="M7" s="19">
+        <f>M5*Assumptions!I$27</f>
+        <v/>
+      </c>
+      <c r="N7" s="19">
+        <f>N5*Assumptions!J$27</f>
+        <v/>
+      </c>
+      <c r="O7" s="19">
+        <f>O5*Assumptions!K$27</f>
         <v/>
       </c>
     </row>
@@ -4795,40 +4816,60 @@
           <t xml:space="preserve">  EBIT margin %</t>
         </is>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="26">
         <f>B7/B5</f>
         <v/>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="26">
         <f>C7/C5</f>
         <v/>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="26">
         <f>D7/D5</f>
         <v/>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="26">
         <f>E7/E5</f>
         <v/>
       </c>
-      <c r="F8" s="14">
+      <c r="F8" s="12">
         <f>F7/F5</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="12">
         <f>G7/G5</f>
         <v/>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="12">
         <f>H7/H5</f>
         <v/>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="12">
         <f>I7/I5</f>
         <v/>
       </c>
-      <c r="J8" s="14">
+      <c r="J8" s="12">
         <f>J7/J5</f>
+        <v/>
+      </c>
+      <c r="K8" s="12">
+        <f>K7/K5</f>
+        <v/>
+      </c>
+      <c r="L8" s="12">
+        <f>L7/L5</f>
+        <v/>
+      </c>
+      <c r="M8" s="12">
+        <f>M7/M5</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>N7/N5</f>
+        <v/>
+      </c>
+      <c r="O8" s="12">
+        <f>O7/O5</f>
         <v/>
       </c>
     </row>
@@ -4838,36 +4879,56 @@
           <t>D&amp;A</t>
         </is>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="25" t="n">
         <v>1849</v>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>1883</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>2007</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>1937</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="19">
         <f>F5*Assumptions!B$28</f>
         <v/>
       </c>
-      <c r="G9" s="13">
+      <c r="G9" s="19">
         <f>G5*Assumptions!C$28</f>
         <v/>
       </c>
-      <c r="H9" s="13">
+      <c r="H9" s="19">
         <f>H5*Assumptions!D$28</f>
         <v/>
       </c>
-      <c r="I9" s="13">
+      <c r="I9" s="19">
         <f>I5*Assumptions!E$28</f>
         <v/>
       </c>
-      <c r="J9" s="13">
+      <c r="J9" s="19">
         <f>J5*Assumptions!F$28</f>
+        <v/>
+      </c>
+      <c r="K9" s="19">
+        <f>K5*Assumptions!G$28</f>
+        <v/>
+      </c>
+      <c r="L9" s="19">
+        <f>L5*Assumptions!H$28</f>
+        <v/>
+      </c>
+      <c r="M9" s="19">
+        <f>M5*Assumptions!I$28</f>
+        <v/>
+      </c>
+      <c r="N9" s="19">
+        <f>N5*Assumptions!J$28</f>
+        <v/>
+      </c>
+      <c r="O9" s="19">
+        <f>O5*Assumptions!K$28</f>
         <v/>
       </c>
     </row>
@@ -4877,40 +4938,60 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="27">
         <f>B7+B9</f>
         <v/>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="27">
         <f>C7+C9</f>
         <v/>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="27">
         <f>D7+D9</f>
         <v/>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="27">
         <f>E7+E9</f>
         <v/>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="19">
         <f>F7+F9</f>
         <v/>
       </c>
-      <c r="G10" s="13">
+      <c r="G10" s="19">
         <f>G7+G9</f>
         <v/>
       </c>
-      <c r="H10" s="13">
+      <c r="H10" s="19">
         <f>H7+H9</f>
         <v/>
       </c>
-      <c r="I10" s="13">
+      <c r="I10" s="19">
         <f>I7+I9</f>
         <v/>
       </c>
-      <c r="J10" s="13">
+      <c r="J10" s="19">
         <f>J7+J9</f>
+        <v/>
+      </c>
+      <c r="K10" s="19">
+        <f>K7+K9</f>
+        <v/>
+      </c>
+      <c r="L10" s="19">
+        <f>L7+L9</f>
+        <v/>
+      </c>
+      <c r="M10" s="19">
+        <f>M7+M9</f>
+        <v/>
+      </c>
+      <c r="N10" s="19">
+        <f>N7+N9</f>
+        <v/>
+      </c>
+      <c r="O10" s="19">
+        <f>O7+O9</f>
         <v/>
       </c>
     </row>
@@ -4920,40 +5001,60 @@
           <t>NOPAT (EBIT×(1−t))</t>
         </is>
       </c>
-      <c r="B11" s="32">
+      <c r="B11" s="28">
         <f>B7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="28">
         <f>C7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="28">
         <f>D7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="28">
         <f>E7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="23">
         <f>F7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="G11" s="27">
+      <c r="G11" s="23">
         <f>G7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="23">
         <f>H7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="23">
         <f>I7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="23">
         <f>J7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="K11" s="23">
+        <f>K7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="L11" s="23">
+        <f>L7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="M11" s="23">
+        <f>M7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="N11" s="23">
+        <f>N7*(1-Assumptions!$B$19)</f>
+        <v/>
+      </c>
+      <c r="O11" s="23">
+        <f>O7*(1-Assumptions!$B$19)</f>
         <v/>
       </c>
     </row>
@@ -4963,36 +5064,56 @@
           <t>Capex</t>
         </is>
       </c>
-      <c r="B12" s="29" t="n">
+      <c r="B12" s="25" t="n">
         <v>1689</v>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>2422</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>2565</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>2949</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="19">
         <f>F5*Assumptions!B$29</f>
         <v/>
       </c>
-      <c r="G12" s="13">
+      <c r="G12" s="19">
         <f>G5*Assumptions!C$29</f>
         <v/>
       </c>
-      <c r="H12" s="13">
+      <c r="H12" s="19">
         <f>H5*Assumptions!D$29</f>
         <v/>
       </c>
-      <c r="I12" s="13">
+      <c r="I12" s="19">
         <f>I5*Assumptions!E$29</f>
         <v/>
       </c>
-      <c r="J12" s="13">
+      <c r="J12" s="19">
         <f>J5*Assumptions!F$29</f>
+        <v/>
+      </c>
+      <c r="K12" s="19">
+        <f>K5*Assumptions!G$29</f>
+        <v/>
+      </c>
+      <c r="L12" s="19">
+        <f>L5*Assumptions!H$29</f>
+        <v/>
+      </c>
+      <c r="M12" s="19">
+        <f>M5*Assumptions!I$29</f>
+        <v/>
+      </c>
+      <c r="N12" s="19">
+        <f>N5*Assumptions!J$29</f>
+        <v/>
+      </c>
+      <c r="O12" s="19">
+        <f>O5*Assumptions!K$29</f>
         <v/>
       </c>
     </row>
@@ -5002,79 +5123,119 @@
           <t>Δ Net working capital</t>
         </is>
       </c>
-      <c r="B13" s="29" t="n">
+      <c r="B13" s="25" t="n">
         <v>5246</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>8355</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>9168</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="19">
         <f>(F5-E5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="G13" s="13">
+      <c r="G13" s="19">
         <f>(G5-F5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="H13" s="13">
+      <c r="H13" s="19">
         <f>(H5-G5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="I13" s="13">
+      <c r="I13" s="19">
         <f>(I5-H5)*Assumptions!$B$30</f>
         <v/>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="19">
         <f>(J5-I5)*Assumptions!$B$30</f>
         <v/>
       </c>
+      <c r="K13" s="19">
+        <f>(K5-J5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="L13" s="19">
+        <f>(L5-K5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="M13" s="19">
+        <f>(M5-L5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="N13" s="19">
+        <f>(N5-M5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
+      <c r="O13" s="19">
+        <f>(O5-N5)*Assumptions!$B$30</f>
+        <v/>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="inlineStr">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>FCFF</t>
         </is>
       </c>
-      <c r="B14" s="33">
+      <c r="B14" s="29">
         <f>B11+B9-B12-B13</f>
         <v/>
       </c>
-      <c r="C14" s="33">
+      <c r="C14" s="29">
         <f>C11+C9-C12-C13</f>
         <v/>
       </c>
-      <c r="D14" s="33">
+      <c r="D14" s="29">
         <f>D11+D9-D12-D13</f>
         <v/>
       </c>
-      <c r="E14" s="33">
+      <c r="E14" s="29">
         <f>E11+E9-E12-E13</f>
         <v/>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="30">
         <f>F11+F9-F12-F13</f>
         <v/>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="30">
         <f>G11+G9-G12-G13</f>
         <v/>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="30">
         <f>H11+H9-H12-H13</f>
         <v/>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="30">
         <f>I11+I9-I12-I13</f>
         <v/>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="30">
         <f>J11+J9-J12-J13</f>
+        <v/>
+      </c>
+      <c r="K14" s="30">
+        <f>K11+K9-K12-K13</f>
+        <v/>
+      </c>
+      <c r="L14" s="30">
+        <f>L11+L9-L12-L13</f>
+        <v/>
+      </c>
+      <c r="M14" s="30">
+        <f>M11+M9-M12-M13</f>
+        <v/>
+      </c>
+      <c r="N14" s="30">
+        <f>N11+N9-N12-N13</f>
+        <v/>
+      </c>
+      <c r="O14" s="30">
+        <f>O11+O9-O12-O13</f>
         <v/>
       </c>
     </row>
@@ -5089,7 +5250,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -5099,6 +5260,11 @@
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5146,6 +5312,31 @@
           <t>FY2030E</t>
         </is>
       </c>
+      <c r="G4" s="10" t="inlineStr">
+        <is>
+          <t>FY2031E</t>
+        </is>
+      </c>
+      <c r="H4" s="10" t="inlineStr">
+        <is>
+          <t>FY2032E</t>
+        </is>
+      </c>
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>FY2033E</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>FY2034E</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>FY2035E</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -5153,24 +5344,44 @@
           <t>FCFF (from Model)</t>
         </is>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="23">
         <f>Model!F14</f>
         <v/>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="23">
         <f>Model!G14</f>
         <v/>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="23">
         <f>Model!H14</f>
         <v/>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="23">
         <f>Model!I14</f>
         <v/>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="23">
         <f>Model!J14</f>
+        <v/>
+      </c>
+      <c r="G5" s="23">
+        <f>Model!K14</f>
+        <v/>
+      </c>
+      <c r="H5" s="23">
+        <f>Model!L14</f>
+        <v/>
+      </c>
+      <c r="I5" s="23">
+        <f>Model!M14</f>
+        <v/>
+      </c>
+      <c r="J5" s="23">
+        <f>Model!N14</f>
+        <v/>
+      </c>
+      <c r="K5" s="23">
+        <f>Model!O14</f>
         <v/>
       </c>
     </row>
@@ -5180,20 +5391,35 @@
           <t>Period (mid-year, t−0.5)</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="31" t="n">
         <v>0.5</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="31" t="n">
         <v>1.5</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="31" t="n">
         <v>2.5</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="31" t="n">
         <v>3.5</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="31" t="n">
         <v>4.5</v>
+      </c>
+      <c r="G6" s="31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H6" s="31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J6" s="31" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="K6" s="31" t="n">
+        <v>9.5</v>
       </c>
     </row>
     <row r="7">
@@ -5202,24 +5428,44 @@
           <t>Discount factor</t>
         </is>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="32">
         <f>1/(1+WACC!$B$10)^B6</f>
         <v/>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="32">
         <f>1/(1+WACC!$B$10)^C6</f>
         <v/>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="32">
         <f>1/(1+WACC!$B$10)^D6</f>
         <v/>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="32">
         <f>1/(1+WACC!$B$10)^E6</f>
         <v/>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="32">
         <f>1/(1+WACC!$B$10)^F6</f>
+        <v/>
+      </c>
+      <c r="G7" s="32">
+        <f>1/(1+WACC!$B$10)^G6</f>
+        <v/>
+      </c>
+      <c r="H7" s="32">
+        <f>1/(1+WACC!$B$10)^H6</f>
+        <v/>
+      </c>
+      <c r="I7" s="32">
+        <f>1/(1+WACC!$B$10)^I6</f>
+        <v/>
+      </c>
+      <c r="J7" s="32">
+        <f>1/(1+WACC!$B$10)^J6</f>
+        <v/>
+      </c>
+      <c r="K7" s="32">
+        <f>1/(1+WACC!$B$10)^K6</f>
         <v/>
       </c>
     </row>
@@ -5229,24 +5475,44 @@
           <t>PV of FCFF</t>
         </is>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="19">
         <f>B5*B7</f>
         <v/>
       </c>
-      <c r="C8" s="13">
+      <c r="C8" s="19">
         <f>C5*C7</f>
         <v/>
       </c>
-      <c r="D8" s="13">
+      <c r="D8" s="19">
         <f>D5*D7</f>
         <v/>
       </c>
-      <c r="E8" s="13">
+      <c r="E8" s="19">
         <f>E5*E7</f>
         <v/>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="19">
         <f>F5*F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="19">
+        <f>G5*G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="19">
+        <f>H5*H7</f>
+        <v/>
+      </c>
+      <c r="I8" s="19">
+        <f>I5*I7</f>
+        <v/>
+      </c>
+      <c r="J8" s="19">
+        <f>J5*J7</f>
+        <v/>
+      </c>
+      <c r="K8" s="19">
+        <f>K5*K7</f>
         <v/>
       </c>
     </row>
@@ -5256,8 +5522,8 @@
           <t>PV of explicit FCFF</t>
         </is>
       </c>
-      <c r="B10" s="13">
-        <f>SUM(B8:F8)</f>
+      <c r="B10" s="19">
+        <f>SUM(B8:K8)</f>
         <v/>
       </c>
     </row>
@@ -5267,8 +5533,8 @@
           <t>Terminal NOPAT (FYn)</t>
         </is>
       </c>
-      <c r="B11" s="27">
-        <f>Model!J11</f>
+      <c r="B11" s="23">
+        <f>Model!O11</f>
         <v/>
       </c>
     </row>
@@ -5278,7 +5544,7 @@
           <t>Invested capital (mm)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
+      <c r="B12" s="18" t="n">
         <v>19868</v>
       </c>
     </row>
@@ -5288,8 +5554,8 @@
           <t>Terminal invested capital (scaled w/ revenue)</t>
         </is>
       </c>
-      <c r="B13" s="27">
-        <f>$B$12*Model!J5/Model!E5</f>
+      <c r="B13" s="23">
+        <f>$B$12*Model!O5/Model!E5</f>
         <v/>
       </c>
     </row>
@@ -5299,7 +5565,7 @@
           <t>Terminal ROIC</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="12">
         <f>MAX($B$11/$B$13,WACC!$B$10)</f>
         <v/>
       </c>
@@ -5310,7 +5576,7 @@
           <t>Terminal reinvestment rate (g/ROIC)</t>
         </is>
       </c>
-      <c r="B15" s="36">
+      <c r="B15" s="33">
         <f>Assumptions!$B$22/$B$14</f>
         <v/>
       </c>
@@ -5321,7 +5587,7 @@
           <t>Terminal value (Gordon)</t>
         </is>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="19">
         <f>$B$11*(1+Assumptions!$B$22)*(1-$B$15)/(WACC!$B$10-Assumptions!$B$22)</f>
         <v/>
       </c>
@@ -5332,8 +5598,8 @@
           <t>PV of terminal value</t>
         </is>
       </c>
-      <c r="B17" s="13">
-        <f>$B$16/(1+WACC!$B$10)^(5-0.5)</f>
+      <c r="B17" s="19">
+        <f>$B$16/(1+WACC!$B$10)^(10-0.5)</f>
         <v/>
       </c>
     </row>
@@ -5343,18 +5609,18 @@
           <t>TV as % of EV</t>
         </is>
       </c>
-      <c r="B18" s="14">
+      <c r="B18" s="12">
         <f>$B$17/($B$10+$B$17)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Enterprise value</t>
         </is>
       </c>
-      <c r="B20" s="23">
+      <c r="B20" s="30">
         <f>$B$10+$B$17</f>
         <v/>
       </c>
@@ -5365,7 +5631,7 @@
           <t>(−) Net debt</t>
         </is>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="23">
         <f>-Assumptions!$B$10</f>
         <v/>
       </c>
@@ -5376,40 +5642,40 @@
           <t>(−) Minority interest</t>
         </is>
       </c>
-      <c r="B22" s="27">
+      <c r="B22" s="23">
         <f>-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="A23" s="13" t="inlineStr">
         <is>
           <t>Equity value</t>
         </is>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="30">
         <f>$B$20-Assumptions!$B$10-Assumptions!$B$9</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="11" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr">
         <is>
           <t>Value per share</t>
         </is>
       </c>
-      <c r="B24" s="37">
+      <c r="B24" s="34">
         <f>$B$23/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="11" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>Upside vs price</t>
         </is>
       </c>
-      <c r="B25" s="38">
+      <c r="B25" s="35">
         <f>$B$24/Assumptions!$B$5-1</f>
         <v/>
       </c>
@@ -5451,149 +5717,149 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="13" t="inlineStr">
         <is>
           <t>WACC \ g</t>
         </is>
       </c>
-      <c r="B4" s="15" t="n">
+      <c r="B4" s="11" t="n">
         <v>0.015</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="11" t="n">
         <v>0.02</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="11" t="n">
         <v>0.025</v>
       </c>
-      <c r="E4" s="15" t="n">
+      <c r="E4" s="11" t="n">
         <v>0.03</v>
       </c>
-      <c r="F4" s="15" t="n">
+      <c r="F4" s="11" t="n">
         <v>0.035</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="n">
-        <v>0.07413267267876338</v>
+      <c r="A5" s="15" t="n">
+        <v>0.06669831282108223</v>
       </c>
       <c r="B5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$5-B$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$5-C$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$5-D$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$5-E$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$5)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$5)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$5-F$4)/(1+$A$5)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="n">
-        <v>0.08163267267876337</v>
+      <c r="A6" s="15" t="n">
+        <v>0.07419831282108222</v>
       </c>
       <c r="B6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$6-B$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$6-C$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$6-D$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$6-E$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$6)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$6)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$6-F$4)/(1+$A$6)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="n">
-        <v>0.08913267267876337</v>
+      <c r="A7" s="15" t="n">
+        <v>0.08169831282108223</v>
       </c>
       <c r="B7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$7-B$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$7-C$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$7-D$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$7-E$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$7)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$7)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$7-F$4)/(1+$A$7)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="n">
-        <v>0.09663267267876338</v>
+      <c r="A8" s="15" t="n">
+        <v>0.08919831282108223</v>
       </c>
       <c r="B8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$8-B$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$8-C$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$8-D$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$8-E$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$8)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$8)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$8-F$4)/(1+$A$8)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="n">
-        <v>0.1041326726787634</v>
+      <c r="A9" s="15" t="n">
+        <v>0.09669831282108222</v>
       </c>
       <c r="B9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+B$4)*(1-B$4/DCF!$B$14)/($A$9-B$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+C$4)*(1-C$4/DCF!$B$14)/($A$9-C$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+D$4)*(1-D$4/DCF!$B$14)/($A$9-D$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+E$4)*(1-E$4/DCF!$B$14)/($A$9-E$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>(SUMPRODUCT(DCF!$B$5:$F$5,1/(1+$A$9)^DCF!$B$6:$F$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(5-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
+        <f>(SUMPRODUCT(DCF!$B$5:$K$5,1/(1+$A$9)^DCF!$B$6:$K$6)+DCF!$B$11*(1+F$4)*(1-F$4/DCF!$B$14)/($A$9-F$4)/(1+$A$9)^(10-0.5)-Assumptions!$B$10-Assumptions!$B$9)/Assumptions!$B$6</f>
         <v/>
       </c>
     </row>
@@ -5629,7 +5895,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As reported by yfinance (USDmm). Hardcoded actuals.</t>
+          <t>As reported by Yahoo snapshot as of 2026-07-08 (USDmm). Hardcoded actuals.</t>
         </is>
       </c>
     </row>
@@ -5671,16 +5937,16 @@
           <t>Tax Effect Of Unusual Items</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="25" t="n">
         <v>-2.52</v>
       </c>
-      <c r="D5" s="29" t="n">
+      <c r="D5" s="25" t="n">
         <v>117.234</v>
       </c>
-      <c r="E5" s="29" t="n">
+      <c r="E5" s="25" t="n">
         <v>14.022</v>
       </c>
-      <c r="F5" s="29" t="n">
+      <c r="F5" s="25" t="n">
         <v>-102.752</v>
       </c>
     </row>
@@ -5690,17 +5956,17 @@
           <t>Tax Rate For Calcs</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
-        <v>2.1e-07</v>
-      </c>
-      <c r="D6" s="29" t="n">
-        <v>3.51e-07</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>1.71e-07</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>3.38e-07</v>
+      <c r="C6" s="25" t="n">
+        <v>2.1e-13</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>3.51e-13</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>1.71e-13</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>3.38e-13</v>
       </c>
     </row>
     <row r="7">
@@ -5709,16 +5975,16 @@
           <t>Normalized EBITDA</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="25" t="n">
         <v>1570</v>
       </c>
-      <c r="D7" s="29" t="n">
+      <c r="D7" s="25" t="n">
         <v>4427</v>
       </c>
-      <c r="E7" s="29" t="n">
+      <c r="E7" s="25" t="n">
         <v>6947</v>
       </c>
-      <c r="F7" s="29" t="n">
+      <c r="F7" s="25" t="n">
         <v>6263</v>
       </c>
     </row>
@@ -5728,16 +5994,16 @@
           <t>Total Unusual Items</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="25" t="n">
         <v>-12</v>
       </c>
-      <c r="D8" s="29" t="n">
+      <c r="D8" s="25" t="n">
         <v>334</v>
       </c>
-      <c r="E8" s="29" t="n">
+      <c r="E8" s="25" t="n">
         <v>82</v>
       </c>
-      <c r="F8" s="29" t="n">
+      <c r="F8" s="25" t="n">
         <v>-304</v>
       </c>
     </row>
@@ -5747,16 +6013,16 @@
           <t>Total Unusual Items Excluding Goodwill</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="25" t="n">
         <v>-12</v>
       </c>
-      <c r="D9" s="29" t="n">
+      <c r="D9" s="25" t="n">
         <v>334</v>
       </c>
-      <c r="E9" s="29" t="n">
+      <c r="E9" s="25" t="n">
         <v>82</v>
       </c>
-      <c r="F9" s="29" t="n">
+      <c r="F9" s="25" t="n">
         <v>-304</v>
       </c>
     </row>
@@ -5766,16 +6032,16 @@
           <t>Net Income From Continuing Operation Net Minority Interest</t>
         </is>
       </c>
-      <c r="C10" s="29" t="n">
+      <c r="C10" s="25" t="n">
         <v>-160</v>
       </c>
-      <c r="D10" s="29" t="n">
+      <c r="D10" s="25" t="n">
         <v>1623</v>
       </c>
-      <c r="E10" s="29" t="n">
+      <c r="E10" s="25" t="n">
         <v>3749</v>
       </c>
-      <c r="F10" s="29" t="n">
+      <c r="F10" s="25" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -5785,16 +6051,16 @@
           <t>Reconciled Depreciation</t>
         </is>
       </c>
-      <c r="C11" s="29" t="n">
+      <c r="C11" s="25" t="n">
         <v>1849</v>
       </c>
-      <c r="D11" s="29" t="n">
+      <c r="D11" s="25" t="n">
         <v>1883</v>
       </c>
-      <c r="E11" s="29" t="n">
+      <c r="E11" s="25" t="n">
         <v>2007</v>
       </c>
-      <c r="F11" s="29" t="n">
+      <c r="F11" s="25" t="n">
         <v>1937</v>
       </c>
     </row>
@@ -5804,16 +6070,16 @@
           <t>Reconciled Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C12" s="29" t="n">
+      <c r="C12" s="25" t="n">
         <v>21545</v>
       </c>
-      <c r="D12" s="29" t="n">
+      <c r="D12" s="25" t="n">
         <v>20899</v>
       </c>
-      <c r="E12" s="29" t="n">
+      <c r="E12" s="25" t="n">
         <v>16694</v>
       </c>
-      <c r="F12" s="29" t="n">
+      <c r="F12" s="25" t="n">
         <v>19888</v>
       </c>
     </row>
@@ -5823,16 +6089,16 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="25" t="n">
         <v>1558</v>
       </c>
-      <c r="D13" s="29" t="n">
+      <c r="D13" s="25" t="n">
         <v>4761</v>
       </c>
-      <c r="E13" s="29" t="n">
+      <c r="E13" s="25" t="n">
         <v>7029</v>
       </c>
-      <c r="F13" s="29" t="n">
+      <c r="F13" s="25" t="n">
         <v>5959</v>
       </c>
     </row>
@@ -5842,16 +6108,16 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="C14" s="29" t="n">
+      <c r="C14" s="25" t="n">
         <v>-291</v>
       </c>
-      <c r="D14" s="29" t="n">
+      <c r="D14" s="25" t="n">
         <v>2878</v>
       </c>
-      <c r="E14" s="29" t="n">
+      <c r="E14" s="25" t="n">
         <v>5022</v>
       </c>
-      <c r="F14" s="29" t="n">
+      <c r="F14" s="25" t="n">
         <v>4022</v>
       </c>
     </row>
@@ -5861,16 +6127,16 @@
           <t>Net Interest Income</t>
         </is>
       </c>
-      <c r="C15" s="29" t="n">
+      <c r="C15" s="25" t="n">
         <v>-251</v>
       </c>
-      <c r="D15" s="29" t="n">
+      <c r="D15" s="25" t="n">
         <v>-431</v>
       </c>
-      <c r="E15" s="29" t="n">
+      <c r="E15" s="25" t="n">
         <v>-506</v>
       </c>
-      <c r="F15" s="29" t="n">
+      <c r="F15" s="25" t="n">
         <v>-511</v>
       </c>
     </row>
@@ -5880,16 +6146,16 @@
           <t>Interest Expense</t>
         </is>
       </c>
-      <c r="C16" s="29" t="n">
+      <c r="C16" s="25" t="n">
         <v>251</v>
       </c>
-      <c r="D16" s="29" t="n">
+      <c r="D16" s="25" t="n">
         <v>431</v>
       </c>
-      <c r="E16" s="29" t="n">
+      <c r="E16" s="25" t="n">
         <v>506</v>
       </c>
-      <c r="F16" s="29" t="n">
+      <c r="F16" s="25" t="n">
         <v>511</v>
       </c>
     </row>
@@ -5899,10 +6165,10 @@
           <t>Interest Income</t>
         </is>
       </c>
-      <c r="B17" s="29" t="n">
+      <c r="B17" s="25" t="n">
         <v>98</v>
       </c>
-      <c r="C17" s="29" t="n">
+      <c r="C17" s="25" t="n">
         <v>93</v>
       </c>
     </row>
@@ -5912,16 +6178,16 @@
           <t>Normalized Income</t>
         </is>
       </c>
-      <c r="C18" s="29" t="n">
+      <c r="C18" s="25" t="n">
         <v>-150.52</v>
       </c>
-      <c r="D18" s="29" t="n">
+      <c r="D18" s="25" t="n">
         <v>1406.234</v>
       </c>
-      <c r="E18" s="29" t="n">
+      <c r="E18" s="25" t="n">
         <v>3681.022</v>
       </c>
-      <c r="F18" s="29" t="n">
+      <c r="F18" s="25" t="n">
         <v>2520.248</v>
       </c>
     </row>
@@ -5931,16 +6197,16 @@
           <t>Net Income From Continuing And Discontinued Operation</t>
         </is>
       </c>
-      <c r="C19" s="29" t="n">
+      <c r="C19" s="25" t="n">
         <v>-160</v>
       </c>
-      <c r="D19" s="29" t="n">
+      <c r="D19" s="25" t="n">
         <v>1623</v>
       </c>
-      <c r="E19" s="29" t="n">
+      <c r="E19" s="25" t="n">
         <v>3749</v>
       </c>
-      <c r="F19" s="29" t="n">
+      <c r="F19" s="25" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -5950,16 +6216,16 @@
           <t>Total Expenses</t>
         </is>
       </c>
-      <c r="C20" s="29" t="n">
+      <c r="C20" s="25" t="n">
         <v>24848</v>
       </c>
-      <c r="D20" s="29" t="n">
+      <c r="D20" s="25" t="n">
         <v>22532</v>
       </c>
-      <c r="E20" s="29" t="n">
+      <c r="E20" s="25" t="n">
         <v>18720</v>
       </c>
-      <c r="F20" s="29" t="n">
+      <c r="F20" s="25" t="n">
         <v>21335</v>
       </c>
     </row>
@@ -5969,16 +6235,16 @@
           <t>Total Operating Income As Reported</t>
         </is>
       </c>
-      <c r="C21" s="29" t="n">
+      <c r="C21" s="25" t="n">
         <v>495</v>
       </c>
-      <c r="D21" s="29" t="n">
+      <c r="D21" s="25" t="n">
         <v>1610</v>
       </c>
-      <c r="E21" s="29" t="n">
+      <c r="E21" s="25" t="n">
         <v>4352</v>
       </c>
-      <c r="F21" s="29" t="n">
+      <c r="F21" s="25" t="n">
         <v>3086</v>
       </c>
     </row>
@@ -5988,16 +6254,16 @@
           <t>Diluted Average Shares</t>
         </is>
       </c>
-      <c r="C22" s="29" t="n">
+      <c r="C22" s="25" t="n">
         <v>327</v>
       </c>
-      <c r="D22" s="29" t="n">
+      <c r="D22" s="25" t="n">
         <v>324</v>
       </c>
-      <c r="E22" s="29" t="n">
+      <c r="E22" s="25" t="n">
         <v>315</v>
       </c>
-      <c r="F22" s="29" t="n">
+      <c r="F22" s="25" t="n">
         <v>314</v>
       </c>
     </row>
@@ -6007,16 +6273,16 @@
           <t>Basic Average Shares</t>
         </is>
       </c>
-      <c r="C23" s="29" t="n">
+      <c r="C23" s="25" t="n">
         <v>327</v>
       </c>
-      <c r="D23" s="29" t="n">
+      <c r="D23" s="25" t="n">
         <v>323</v>
       </c>
-      <c r="E23" s="29" t="n">
+      <c r="E23" s="25" t="n">
         <v>315</v>
       </c>
-      <c r="F23" s="29" t="n">
+      <c r="F23" s="25" t="n">
         <v>313</v>
       </c>
     </row>
@@ -6026,17 +6292,17 @@
           <t>Diluted EPS</t>
         </is>
       </c>
-      <c r="C24" s="29" t="n">
-        <v>-4.892969999999999e-07</v>
-      </c>
-      <c r="D24" s="29" t="n">
-        <v>5.009999999999999e-06</v>
-      </c>
-      <c r="E24" s="29" t="n">
-        <v>1.189e-05</v>
-      </c>
-      <c r="F24" s="29" t="n">
-        <v>7.4e-06</v>
+      <c r="C24" s="25" t="n">
+        <v>-4.892969999999999e-13</v>
+      </c>
+      <c r="D24" s="25" t="n">
+        <v>5.009999999999998e-12</v>
+      </c>
+      <c r="E24" s="25" t="n">
+        <v>1.189e-11</v>
+      </c>
+      <c r="F24" s="25" t="n">
+        <v>7.4e-12</v>
       </c>
     </row>
     <row r="25">
@@ -6045,17 +6311,17 @@
           <t>Basic EPS</t>
         </is>
       </c>
-      <c r="C25" s="29" t="n">
-        <v>-4.892969999999999e-07</v>
-      </c>
-      <c r="D25" s="29" t="n">
-        <v>5.019999999999999e-06</v>
-      </c>
-      <c r="E25" s="29" t="n">
-        <v>1.191e-05</v>
-      </c>
-      <c r="F25" s="29" t="n">
-        <v>7.4e-06</v>
+      <c r="C25" s="25" t="n">
+        <v>-4.892969999999999e-13</v>
+      </c>
+      <c r="D25" s="25" t="n">
+        <v>5.019999999999999e-12</v>
+      </c>
+      <c r="E25" s="25" t="n">
+        <v>1.191e-11</v>
+      </c>
+      <c r="F25" s="25" t="n">
+        <v>7.4e-12</v>
       </c>
     </row>
     <row r="26">
@@ -6064,16 +6330,16 @@
           <t>Diluted NI Availto Com Stockholders</t>
         </is>
       </c>
-      <c r="C26" s="29" t="n">
+      <c r="C26" s="25" t="n">
         <v>-160</v>
       </c>
-      <c r="D26" s="29" t="n">
+      <c r="D26" s="25" t="n">
         <v>1623</v>
       </c>
-      <c r="E26" s="29" t="n">
+      <c r="E26" s="25" t="n">
         <v>3749</v>
       </c>
-      <c r="F26" s="29" t="n">
+      <c r="F26" s="25" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -6083,16 +6349,16 @@
           <t>Net Income Common Stockholders</t>
         </is>
       </c>
-      <c r="C27" s="29" t="n">
+      <c r="C27" s="25" t="n">
         <v>-160</v>
       </c>
-      <c r="D27" s="29" t="n">
+      <c r="D27" s="25" t="n">
         <v>1623</v>
       </c>
-      <c r="E27" s="29" t="n">
+      <c r="E27" s="25" t="n">
         <v>3749</v>
       </c>
-      <c r="F27" s="29" t="n">
+      <c r="F27" s="25" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -6102,16 +6368,16 @@
           <t>Net Income</t>
         </is>
       </c>
-      <c r="C28" s="29" t="n">
+      <c r="C28" s="25" t="n">
         <v>-160</v>
       </c>
-      <c r="D28" s="29" t="n">
+      <c r="D28" s="25" t="n">
         <v>1623</v>
       </c>
-      <c r="E28" s="29" t="n">
+      <c r="E28" s="25" t="n">
         <v>3749</v>
       </c>
-      <c r="F28" s="29" t="n">
+      <c r="F28" s="25" t="n">
         <v>2319</v>
       </c>
     </row>
@@ -6121,16 +6387,16 @@
           <t>Minority Interests</t>
         </is>
       </c>
-      <c r="C29" s="29" t="n">
+      <c r="C29" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="D29" s="29" t="n">
+      <c r="D29" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="E29" s="29" t="n">
+      <c r="E29" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="F29" s="29" t="n">
+      <c r="F29" s="25" t="n">
         <v>-4</v>
       </c>
     </row>
@@ -6140,16 +6406,16 @@
           <t>Net Income Including Noncontrolling Interests</t>
         </is>
       </c>
-      <c r="C30" s="29" t="n">
+      <c r="C30" s="25" t="n">
         <v>-167</v>
       </c>
-      <c r="D30" s="29" t="n">
+      <c r="D30" s="25" t="n">
         <v>1577</v>
       </c>
-      <c r="E30" s="29" t="n">
+      <c r="E30" s="25" t="n">
         <v>3738</v>
       </c>
-      <c r="F30" s="29" t="n">
+      <c r="F30" s="25" t="n">
         <v>2323</v>
       </c>
     </row>
@@ -6159,16 +6425,16 @@
           <t>Net Income Continuous Operations</t>
         </is>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="25" t="n">
         <v>-167</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="25" t="n">
         <v>1577</v>
       </c>
-      <c r="E31" s="29" t="n">
+      <c r="E31" s="25" t="n">
         <v>3738</v>
       </c>
-      <c r="F31" s="29" t="n">
+      <c r="F31" s="25" t="n">
         <v>2323</v>
       </c>
     </row>
@@ -6178,16 +6444,16 @@
           <t>Earnings From Equity Interest Net Of Tax</t>
         </is>
       </c>
-      <c r="C32" s="29" t="n">
+      <c r="C32" s="25" t="n">
         <v>-13</v>
       </c>
-      <c r="D32" s="29" t="n">
+      <c r="D32" s="25" t="n">
         <v>-11</v>
       </c>
-      <c r="E32" s="29" t="n">
+      <c r="E32" s="25" t="n">
         <v>-4</v>
       </c>
-      <c r="F32" s="29" t="n">
+      <c r="F32" s="25" t="n">
         <v>-1</v>
       </c>
     </row>
@@ -6197,16 +6463,16 @@
           <t>Tax Provision</t>
         </is>
       </c>
-      <c r="C33" s="29" t="n">
+      <c r="C33" s="25" t="n">
         <v>-388</v>
       </c>
-      <c r="D33" s="29" t="n">
+      <c r="D33" s="25" t="n">
         <v>859</v>
       </c>
-      <c r="E33" s="29" t="n">
+      <c r="E33" s="25" t="n">
         <v>774</v>
       </c>
-      <c r="F33" s="29" t="n">
+      <c r="F33" s="25" t="n">
         <v>1187</v>
       </c>
     </row>
@@ -6216,16 +6482,16 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="C34" s="29" t="n">
+      <c r="C34" s="25" t="n">
         <v>-542</v>
       </c>
-      <c r="D34" s="29" t="n">
+      <c r="D34" s="25" t="n">
         <v>2447</v>
       </c>
-      <c r="E34" s="29" t="n">
+      <c r="E34" s="25" t="n">
         <v>4516</v>
       </c>
-      <c r="F34" s="29" t="n">
+      <c r="F34" s="25" t="n">
         <v>3511</v>
       </c>
     </row>
@@ -6235,16 +6501,16 @@
           <t>Other Income Expense</t>
         </is>
       </c>
-      <c r="C35" s="29" t="n">
+      <c r="C35" s="25" t="n">
         <v>117</v>
       </c>
-      <c r="D35" s="29" t="n">
+      <c r="D35" s="25" t="n">
         <v>492</v>
       </c>
-      <c r="E35" s="29" t="n">
+      <c r="E35" s="25" t="n">
         <v>174</v>
       </c>
-      <c r="F35" s="29" t="n">
+      <c r="F35" s="25" t="n">
         <v>-176</v>
       </c>
     </row>
@@ -6254,16 +6520,16 @@
           <t>Other Non Operating Income Expenses</t>
         </is>
       </c>
-      <c r="C36" s="29" t="n">
+      <c r="C36" s="25" t="n">
         <v>129</v>
       </c>
-      <c r="D36" s="29" t="n">
+      <c r="D36" s="25" t="n">
         <v>158</v>
       </c>
-      <c r="E36" s="29" t="n">
+      <c r="E36" s="25" t="n">
         <v>92</v>
       </c>
-      <c r="F36" s="29" t="n">
+      <c r="F36" s="25" t="n">
         <v>128</v>
       </c>
     </row>
@@ -6273,16 +6539,16 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="C37" s="29" t="n">
+      <c r="C37" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D37" s="29" t="n">
+      <c r="D37" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="E37" s="29" t="n">
+      <c r="E37" s="25" t="n">
         <v>71</v>
       </c>
-      <c r="F37" s="29" t="n">
+      <c r="F37" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6292,16 +6558,16 @@
           <t>Gain On Sale Of Ppe</t>
         </is>
       </c>
-      <c r="C38" s="29" t="n">
+      <c r="C38" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="D38" s="29" t="n">
+      <c r="D38" s="25" t="n">
         <v>27</v>
       </c>
-      <c r="E38" s="29" t="n">
+      <c r="E38" s="25" t="n">
         <v>71</v>
       </c>
-      <c r="F38" s="29" t="n">
+      <c r="F38" s="25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -6311,16 +6577,16 @@
           <t>Gain On Sale Of Security</t>
         </is>
       </c>
-      <c r="C39" s="29" t="n">
+      <c r="C39" s="25" t="n">
         <v>-13</v>
       </c>
-      <c r="D39" s="29" t="n">
+      <c r="D39" s="25" t="n">
         <v>307</v>
       </c>
-      <c r="E39" s="29" t="n">
+      <c r="E39" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="F39" s="29" t="n">
+      <c r="F39" s="25" t="n">
         <v>-304</v>
       </c>
     </row>
@@ -6330,16 +6596,16 @@
           <t>Net Non Operating Interest Income Expense</t>
         </is>
       </c>
-      <c r="C40" s="29" t="n">
+      <c r="C40" s="25" t="n">
         <v>-251</v>
       </c>
-      <c r="D40" s="29" t="n">
+      <c r="D40" s="25" t="n">
         <v>-431</v>
       </c>
-      <c r="E40" s="29" t="n">
+      <c r="E40" s="25" t="n">
         <v>-506</v>
       </c>
-      <c r="F40" s="29" t="n">
+      <c r="F40" s="25" t="n">
         <v>-511</v>
       </c>
     </row>
@@ -6349,16 +6615,16 @@
           <t>Interest Expense Non Operating</t>
         </is>
       </c>
-      <c r="C41" s="29" t="n">
+      <c r="C41" s="25" t="n">
         <v>251</v>
       </c>
-      <c r="D41" s="29" t="n">
+      <c r="D41" s="25" t="n">
         <v>431</v>
       </c>
-      <c r="E41" s="29" t="n">
+      <c r="E41" s="25" t="n">
         <v>506</v>
       </c>
-      <c r="F41" s="29" t="n">
+      <c r="F41" s="25" t="n">
         <v>511</v>
       </c>
     </row>
@@ -6368,10 +6634,10 @@
           <t>Interest Income Non Operating</t>
         </is>
       </c>
-      <c r="B42" s="29" t="n">
+      <c r="B42" s="25" t="n">
         <v>98</v>
       </c>
-      <c r="C42" s="29" t="n">
+      <c r="C42" s="25" t="n">
         <v>93</v>
       </c>
     </row>
@@ -6381,16 +6647,16 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="C43" s="29" t="n">
+      <c r="C43" s="25" t="n">
         <v>-408</v>
       </c>
-      <c r="D43" s="29" t="n">
+      <c r="D43" s="25" t="n">
         <v>2386</v>
       </c>
-      <c r="E43" s="29" t="n">
+      <c r="E43" s="25" t="n">
         <v>4848</v>
       </c>
-      <c r="F43" s="29" t="n">
+      <c r="F43" s="25" t="n">
         <v>4198</v>
       </c>
     </row>
@@ -6400,16 +6666,16 @@
           <t>Operating Expense</t>
         </is>
       </c>
-      <c r="C44" s="29" t="n">
+      <c r="C44" s="25" t="n">
         <v>2545</v>
       </c>
-      <c r="D44" s="29" t="n">
+      <c r="D44" s="25" t="n">
         <v>846</v>
       </c>
-      <c r="E44" s="29" t="n">
+      <c r="E44" s="25" t="n">
         <v>1142</v>
       </c>
-      <c r="F44" s="29" t="n">
+      <c r="F44" s="25" t="n">
         <v>495</v>
       </c>
     </row>
@@ -6419,16 +6685,16 @@
           <t>Other Operating Expenses</t>
         </is>
       </c>
-      <c r="C45" s="29" t="n">
+      <c r="C45" s="25" t="n">
         <v>902</v>
       </c>
-      <c r="D45" s="29" t="n">
+      <c r="D45" s="25" t="n">
         <v>-803</v>
       </c>
-      <c r="E45" s="29" t="n">
+      <c r="E45" s="25" t="n">
         <v>-567</v>
       </c>
-      <c r="F45" s="29" t="n">
+      <c r="F45" s="25" t="n">
         <v>-1112</v>
       </c>
     </row>
@@ -6438,16 +6704,16 @@
           <t>Other Taxes</t>
         </is>
       </c>
-      <c r="C46" s="29" t="n">
+      <c r="C46" s="25" t="n">
         <v>552</v>
       </c>
-      <c r="D46" s="29" t="n">
+      <c r="D46" s="25" t="n">
         <v>553</v>
       </c>
-      <c r="E46" s="29" t="n">
+      <c r="E46" s="25" t="n">
         <v>586</v>
       </c>
-      <c r="F46" s="29" t="n">
+      <c r="F46" s="25" t="n">
         <v>622</v>
       </c>
     </row>
@@ -6457,16 +6723,16 @@
           <t>Depreciation Amortization Depletion Income Statement</t>
         </is>
       </c>
-      <c r="C47" s="29" t="n">
+      <c r="C47" s="25" t="n">
         <v>1091</v>
       </c>
-      <c r="D47" s="29" t="n">
+      <c r="D47" s="25" t="n">
         <v>1096</v>
       </c>
-      <c r="E47" s="29" t="n">
+      <c r="E47" s="25" t="n">
         <v>1123</v>
       </c>
-      <c r="F47" s="29" t="n">
+      <c r="F47" s="25" t="n">
         <v>985</v>
       </c>
     </row>
@@ -6476,16 +6742,16 @@
           <t>Depreciation And Amortization In Income Statement</t>
         </is>
       </c>
-      <c r="C48" s="29" t="n">
+      <c r="C48" s="25" t="n">
         <v>1091</v>
       </c>
-      <c r="D48" s="29" t="n">
+      <c r="D48" s="25" t="n">
         <v>1096</v>
       </c>
-      <c r="E48" s="29" t="n">
+      <c r="E48" s="25" t="n">
         <v>1123</v>
       </c>
-      <c r="F48" s="29" t="n">
+      <c r="F48" s="25" t="n">
         <v>985</v>
       </c>
     </row>
@@ -6495,13 +6761,13 @@
           <t>Selling General And Administration</t>
         </is>
       </c>
-      <c r="B49" s="29" t="n">
+      <c r="B49" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C49" s="29" t="n">
+      <c r="C49" s="25" t="n">
         <v>-110</v>
       </c>
-      <c r="D49" s="29" t="n">
+      <c r="D49" s="25" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -6511,10 +6777,10 @@
           <t>General And Administrative Expense</t>
         </is>
       </c>
-      <c r="C50" s="29" t="n">
+      <c r="C50" s="25" t="n">
         <v>-110</v>
       </c>
-      <c r="D50" s="29" t="n">
+      <c r="D50" s="25" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -6524,13 +6790,13 @@
           <t>Salaries And Wages</t>
         </is>
       </c>
-      <c r="B51" s="29" t="n">
+      <c r="B51" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="C51" s="29" t="n">
+      <c r="C51" s="25" t="n">
         <v>-110</v>
       </c>
-      <c r="D51" s="29" t="n">
+      <c r="D51" s="25" t="n">
         <v>-54</v>
       </c>
     </row>
@@ -6540,16 +6806,16 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="C52" s="29" t="n">
+      <c r="C52" s="25" t="n">
         <v>2137</v>
       </c>
-      <c r="D52" s="29" t="n">
+      <c r="D52" s="25" t="n">
         <v>3232</v>
       </c>
-      <c r="E52" s="29" t="n">
+      <c r="E52" s="25" t="n">
         <v>5990</v>
       </c>
-      <c r="F52" s="29" t="n">
+      <c r="F52" s="25" t="n">
         <v>4693</v>
       </c>
     </row>
@@ -6559,16 +6825,16 @@
           <t>Cost Of Revenue</t>
         </is>
       </c>
-      <c r="C53" s="29" t="n">
+      <c r="C53" s="25" t="n">
         <v>22303</v>
       </c>
-      <c r="D53" s="29" t="n">
+      <c r="D53" s="25" t="n">
         <v>21686</v>
       </c>
-      <c r="E53" s="29" t="n">
+      <c r="E53" s="25" t="n">
         <v>17578</v>
       </c>
-      <c r="F53" s="29" t="n">
+      <c r="F53" s="25" t="n">
         <v>20840</v>
       </c>
     </row>
@@ -6578,16 +6844,16 @@
           <t>Total Revenue</t>
         </is>
       </c>
-      <c r="C54" s="29" t="n">
+      <c r="C54" s="25" t="n">
         <v>24440</v>
       </c>
-      <c r="D54" s="29" t="n">
+      <c r="D54" s="25" t="n">
         <v>24918</v>
       </c>
-      <c r="E54" s="29" t="n">
+      <c r="E54" s="25" t="n">
         <v>23568</v>
       </c>
-      <c r="F54" s="29" t="n">
+      <c r="F54" s="25" t="n">
         <v>25533</v>
       </c>
     </row>
@@ -6597,16 +6863,16 @@
           <t>Operating Revenue</t>
         </is>
       </c>
-      <c r="C55" s="29" t="n">
+      <c r="C55" s="25" t="n">
         <v>24440</v>
       </c>
-      <c r="D55" s="29" t="n">
+      <c r="D55" s="25" t="n">
         <v>24918</v>
       </c>
-      <c r="E55" s="29" t="n">
+      <c r="E55" s="25" t="n">
         <v>23568</v>
       </c>
-      <c r="F55" s="29" t="n">
+      <c r="F55" s="25" t="n">
         <v>25533</v>
       </c>
     </row>

--- a/docs/reports/CEG.xlsx
+++ b/docs/reports/CEG.xlsx
@@ -611,7 +611,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>278.3245544984664</v>
+        <v>287.6053226429142</v>
       </c>
     </row>
     <row r="8">
@@ -3342,13 +3342,13 @@
         </is>
       </c>
       <c r="C5" s="6" t="n">
-        <v>282.7568220272482</v>
+        <v>308.6010328571111</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>231.7571806850097</v>
+        <v>253.8704510719582</v>
       </c>
       <c r="E5" s="6" t="n">
-        <v>340.6284356626006</v>
+        <v>370.435085929282</v>
       </c>
       <c r="F5" s="11" t="n">
         <v>0.3888888888888889</v>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>278.3245544984664</v>
+        <v>287.6053226429142</v>
       </c>
     </row>
     <row r="20">
@@ -3531,7 +3531,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Target anchored 15% to the Street consensus ($357.81); model-only target $264.30.</t>
+          <t>Target anchored 15% to the Street consensus ($357.81); model-only target $275.22.</t>
         </is>
       </c>
     </row>
@@ -3643,31 +3643,31 @@
         <v>35620</v>
       </c>
       <c r="C5" s="19" t="n">
-        <v>41489.81542106217</v>
+        <v>41038.19777777778</v>
       </c>
       <c r="D5" s="19" t="n">
-        <v>46684.81047221891</v>
+        <v>46628.51227506173</v>
       </c>
       <c r="E5" s="19" t="n">
-        <v>51205.70282363475</v>
+        <v>52239.47658549417</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>55122.88947284904</v>
+        <v>57695.59969553466</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>58535.99793296073</v>
+        <v>62804.86557968367</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>61548.58653522813</v>
+        <v>67368.68581180734</v>
       </c>
       <c r="I5" s="19" t="n">
-        <v>64255.02592469643</v>
+        <v>71193.73008401108</v>
       </c>
       <c r="J5" s="19" t="n">
-        <v>66735.31941725372</v>
+        <v>74104.76260300176</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>68403.70240268506</v>
+        <v>75957.38166807679</v>
       </c>
     </row>
     <row r="6">
@@ -3812,31 +3812,31 @@
         <v>4849.44539086</v>
       </c>
       <c r="C9" s="19" t="n">
-        <v>5590.764766857072</v>
+        <v>5525.942372038404</v>
       </c>
       <c r="D9" s="19" t="n">
-        <v>6203.789146643189</v>
+        <v>6195.86839758891</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>6694.369018542216</v>
+        <v>6836.876525028457</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>7077.754170234815</v>
+        <v>7425.097588797129</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>7372.257776958407</v>
+        <v>7936.472619359384</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>7595.569202017806</v>
+        <v>8348.274741251849</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>7763.038830619873</v>
+        <v>8640.698949123916</v>
       </c>
       <c r="J9" s="19" t="n">
-        <v>8076.765231201512</v>
+        <v>9008.908500493353</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>8287.795010694002</v>
+        <v>9243.241861718139</v>
       </c>
     </row>
     <row r="10">
@@ -3896,31 +3896,31 @@
         <v>4115.400504666752</v>
       </c>
       <c r="C12" s="20" t="n">
-        <v>4811.06573334487</v>
+        <v>4756.111588430245</v>
       </c>
       <c r="D12" s="20" t="n">
-        <v>5392.656677636085</v>
+        <v>5384.283510478498</v>
       </c>
       <c r="E12" s="20" t="n">
-        <v>5875.97646236353</v>
+        <v>5998.403661299346</v>
       </c>
       <c r="F12" s="20" t="n">
-        <v>6272.366069495353</v>
+        <v>6577.289264433131</v>
       </c>
       <c r="G12" s="20" t="n">
-        <v>6596.361548848513</v>
+        <v>7098.836841614328</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>6862.441300134499</v>
+        <v>7541.310292272473</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>7083.430048819514</v>
+        <v>7884.757567208794</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>7459.544752551667</v>
+        <v>8322.970905373859</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>7747.887269074251</v>
+        <v>8643.713225763035</v>
       </c>
     </row>
     <row r="13">
@@ -4254,28 +4254,28 @@
         <v>0.3950573767281558</v>
       </c>
       <c r="C26" s="11" t="n">
-        <v>0.1647898770651929</v>
+        <v>0.1521111111111111</v>
       </c>
       <c r="D26" s="11" t="n">
-        <v>0.125211331948214</v>
+        <v>0.1362222222222222</v>
       </c>
       <c r="E26" s="11" t="n">
-        <v>0.09683861422348755</v>
+        <v>0.1203333333333333</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>0.07649903102992379</v>
+        <v>0.1044444444444445</v>
       </c>
       <c r="G26" s="11" t="n">
-        <v>0.06191817034179282</v>
+        <v>0.08855555555555555</v>
       </c>
       <c r="H26" s="11" t="n">
-        <v>0.05146557176180035</v>
+        <v>0.07266666666666667</v>
       </c>
       <c r="I26" s="11" t="n">
-        <v>0.04397240524636979</v>
+        <v>0.05677777777777777</v>
       </c>
       <c r="J26" s="11" t="n">
-        <v>0.03860077024113361</v>
+        <v>0.04088888888888889</v>
       </c>
       <c r="K26" s="11" t="n">
         <v>0.025</v>
